--- a/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H290"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1452,7 +1452,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.bold.composed[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.composed[1]</t>
+          <t xml:space="preserve">ahead.bold.composed[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1477,14 +1477,14 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めない。…必ず返す</t>
+          <t xml:space="preserve">…片付いた相手だよ。…なのに、まだ目で追ってる</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.bold.composed[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.composed[1]</t>
+          <t xml:space="preserve">behind.bold.composed[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1509,14 +1509,14 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった。もう振り返らない</t>
+          <t xml:space="preserve">…終わった話らしいね。…じゃあ、この重さは何なんだろう</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.bold.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold.composed[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…完敗。…でも悔いはないよ</t>
+          <t xml:space="preserve">…認めない。…必ず返す</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold.composed[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
@@ -1573,14 +1573,14 @@
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の相手だった。…これからもよろしく</t>
+          <t xml:space="preserve">…終わった。もう振り返らない</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.bold.composed[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.composed[1]</t>
+          <t xml:space="preserve">loser.bold.composed[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1605,14 +1605,14 @@
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この日を待ってた。…終わらせるよ</t>
+          <t xml:space="preserve">…完敗。…でも悔いはないよ</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold.composed[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.composed[1]</t>
+          <t xml:space="preserve">winner.bold.composed[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1637,14 +1637,14 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…同感だね。本気で行くよ</t>
+          <t xml:space="preserve">…最高の相手だった。…これからもよろしく</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold.composed[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
@@ -1669,14 +1669,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全部出す。今日で</t>
+          <t xml:space="preserve">…この日を待ってた。…終わらせるよ</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold.composed[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
@@ -1701,14 +1701,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うん。受けて立つ</t>
+          <t xml:space="preserve">…同感だね。本気で行くよ</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold.composed[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
@@ -1733,14 +1733,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃がす気はないよ。今日で終わらせる</t>
+          <t xml:space="preserve">…全部出す。今日で</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold.composed[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
@@ -1765,14 +1765,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…受けて立つよ。好きにおいで</t>
+          <t xml:space="preserve">…うん。受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold.composed[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.bold.composed[1]</t>
+          <t xml:space="preserve">attacker.bold.composed[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1797,14 +1797,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後だね。…全部出すよ</t>
+          <t xml:space="preserve">…逃がす気はないよ。今日で終わらせる</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold.composed[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.bold.composed[1]</t>
+          <t xml:space="preserve">defender.bold.composed[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1829,14 +1829,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかってる。全力でおいで</t>
+          <t xml:space="preserve">…受けて立つよ。好きにおいで</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.bold.composed[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.bold.composed[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この借り、返すよ</t>
+          <t xml:space="preserve">…最後だね。…全部出すよ</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.bold.composed[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.composed[1]</t>
+          <t xml:space="preserve">fateDefender.bold.composed[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1893,14 +1893,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…通過点だね。まだ先がある</t>
+          <t xml:space="preserve">…わかってる。全力でおいで</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.bold.composed[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.bold.composed[1]</t>
+          <t xml:space="preserve">loserLines.bold.composed[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1925,14 +1925,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…届かなかった。…でも、次は変える</t>
+          <t xml:space="preserve">…この借り、返すよ</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold.composed[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.bold.composed[1]</t>
+          <t xml:space="preserve">winnerLines.bold.composed[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1957,14 +1957,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やっと一つ。…でも、まだ先がある</t>
+          <t xml:space="preserve">…通過点だね。まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.bold.composed[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.composed[1]</t>
+          <t xml:space="preserve">fateLoser.bold.composed[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1989,14 +1989,14 @@
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…完敗だね。…でも、次がある</t>
+          <t xml:space="preserve">…届かなかった。…でも、次は変える</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.bold.composed[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.composed[1]</t>
+          <t xml:space="preserve">fateWinner.bold.composed[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2021,14 +2021,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ勝った。…でもまだ先があるだろうね</t>
+          <t xml:space="preserve">…やっと一つ。…でも、まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold.composed[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.composed[1]</t>
+          <t xml:space="preserve">loser.bold.composed[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2053,14 +2053,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めない。…こんな結果は</t>
+          <t xml:space="preserve">…完敗だね。…でも、次がある</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold.composed[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.composed[1]</t>
+          <t xml:space="preserve">winner.bold.composed[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2085,14 +2085,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ようやく。…超えたよ</t>
+          <t xml:space="preserve">…一つ勝った。…でもまだ先があるだろうね</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold.composed[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.bold.composed[1]</t>
+          <t xml:space="preserve">loserLines.bold.composed[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2117,14 +2117,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が静かに{nameA}の前に立った。「…もういいだろう。受けて立つよ」</t>
+          <t xml:space="preserve">…認めない。…こんな結果は</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.bold.composed[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2134,29 +2134,29 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.lose[1]</t>
+          <t xml:space="preserve">winnerLines.bold.composed[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたよ。……言い訳はしない。</t>
+          <t xml:space="preserve">…ようやく。…超えたよ</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold.composed[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2166,29 +2166,29 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.lose[2]</t>
+          <t xml:space="preserve">awakening.bold.composed[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……届かなかったね。ごめん、社長。</t>
+          <t xml:space="preserve">{nameB}が静かに{nameA}の前に立った。「…もういいだろう。受けて立つよ」</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.lose[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.lose[3]</t>
+          <t xml:space="preserve">composed_bold.lose[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2213,14 +2213,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗。……悔しいよ、さすがに。</t>
+          <t xml:space="preserve">負けたよ。……言い訳はしない。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.lose[2]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.petition[1]</t>
+          <t xml:space="preserve">composed_bold.lose[2]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2245,14 +2245,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。……あの人は、私が引き受けるよ。</t>
+          <t xml:space="preserve">……届かなかったね。ごめん、社長。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.lose[3]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.petition[2]</t>
+          <t xml:space="preserve">composed_bold.lose[3]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2277,14 +2277,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頼みがあるの。あの相手と、やらせてほしい。</t>
+          <t xml:space="preserve">完敗。……悔しいよ、さすがに。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.petition[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.petition[3]</t>
+          <t xml:space="preserve">composed_bold.petition[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……名前を挙げさせてもらうね。あの人と、やりたい。</t>
+          <t xml:space="preserve">社長。……あの人は、私が引き受けるよ。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.petition[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.sendoff[1]</t>
+          <t xml:space="preserve">composed_bold.petition[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2341,14 +2341,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとう。……ちゃんと応えるよ。</t>
+          <t xml:space="preserve">頼みがあるの。あの相手と、やらせてほしい。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.petition[3]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.sendoff[2]</t>
+          <t xml:space="preserve">composed_bold.petition[3]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2373,14 +2373,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……話が早いね。感謝する。行ってくる。</t>
+          <t xml:space="preserve">……名前を挙げさせてもらうね。あの人と、やりたい。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.sendoff[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.sendoff[3]</t>
+          <t xml:space="preserve">composed_bold.sendoff[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2405,14 +2405,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うん、ありがとう。……心配は要らないから。</t>
+          <t xml:space="preserve">ありがとう。……ちゃんと応えるよ。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.sendoff[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.win[1]</t>
+          <t xml:space="preserve">composed_bold.sendoff[2]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2437,14 +2437,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ってきたよ。……通してくれて、ありがとう。</t>
+          <t xml:space="preserve">……話が早いね。感謝する。行ってくる。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.sendoff[3]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.win[2]</t>
+          <t xml:space="preserve">composed_bold.sendoff[3]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2469,14 +2469,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ほら、任せて正解だったでしょ。</t>
+          <t xml:space="preserve">うん、ありがとう。……心配は要らないから。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.win[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.win[3]</t>
+          <t xml:space="preserve">composed_bold.win[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったよ。思った通りにね。……感謝してる。</t>
+          <t xml:space="preserve">勝ってきたよ。……通してくれて、ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.win[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold._accept[1]</t>
+          <t xml:space="preserve">composed_bold.win[2]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2533,14 +2533,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来なよ。……受けて立つから。</t>
+          <t xml:space="preserve">……ほら、任せて正解だったでしょ。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_bold.win[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold._accept[2]</t>
+          <t xml:space="preserve">composed_bold.win[3]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2565,14 +2565,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい度胸してるね。乗ってあげる。</t>
+          <t xml:space="preserve">勝ったよ。思った通りにね。……感謝してる。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold._accept[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold._accept[3]</t>
+          <t xml:space="preserve">composed_bold._accept[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2597,14 +2597,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだんだ。……せいぜい、悔やまないように。</t>
+          <t xml:space="preserve">来なよ。……受けて立つから。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold._accept[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.draw[1]</t>
+          <t xml:space="preserve">composed_bold._accept[2]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2629,14 +2629,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……決めきれなかったか。つまらないね。</t>
+          <t xml:space="preserve">……いい度胸してるね。乗ってあげる。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold._accept[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.draw[2]</t>
+          <t xml:space="preserve">composed_bold._accept[3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2661,14 +2661,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けは、わたしの趣味じゃない。</t>
+          <t xml:space="preserve">わたしを選んだんだ。……せいぜい、悔やまないように。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.draw[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.draw[3]</t>
+          <t xml:space="preserve">composed_bold.draw[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2693,14 +2693,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……まだ足りない。また名前を呼びなよ。</t>
+          <t xml:space="preserve">……決めきれなかったか。つまらないね。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.draw[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.lose[1]</t>
+          <t xml:space="preserve">composed_bold.draw[2]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2725,14 +2725,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……持っていかれたか。大きく出た分、堪えるね。</t>
+          <t xml:space="preserve">こういう終わり方は、わたしの趣味じゃない。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.draw[3]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.lose[2]</t>
+          <t xml:space="preserve">composed_bold.draw[3]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたが上だった。……認めるよ、今日は。</t>
+          <t xml:space="preserve">……まだ足りない。また名前を呼びなよ。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.lose[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.lose[3]</t>
+          <t xml:space="preserve">composed_bold.lose[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2789,14 +2789,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いい仕事するね。次は、こうはいかない。</t>
+          <t xml:space="preserve">……持っていかれたか。大きく出た分、堪えるね。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.lose[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.win[1]</t>
+          <t xml:space="preserve">composed_bold.lose[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2821,14 +2821,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ほら、言った通りだろ。</t>
+          <t xml:space="preserve">あんたが上だった。……認めるよ、今日は。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.lose[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.win[2]</t>
+          <t xml:space="preserve">composed_bold.lose[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2853,14 +2853,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだのが、間違いだったね。</t>
+          <t xml:space="preserve">……いい仕事するね。次は、こうはいかない。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.win[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_bold.win[3]</t>
+          <t xml:space="preserve">composed_bold.win[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2885,14 +2885,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかったよ。もう一度来るなら、受ける。</t>
+          <t xml:space="preserve">……ほら、言った通りだろ。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.bold.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.win[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2902,29 +2902,29 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.bold.composed[1]</t>
+          <t xml:space="preserve">composed_bold.win[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ終わりじゃないよ。…やってみせる</t>
+          <t xml:space="preserve">わたしを選んだのが、間違いだったね。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_bold.win[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2934,29 +2934,29 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold.composed[1]</t>
+          <t xml:space="preserve">composed_bold.win[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう一シーズンだけ。…結果は出すよ</t>
+          <t xml:space="preserve">……悪くなかったよ。もう一度来るなら、受ける。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.bold.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.composed[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.bold.composed[1]</t>
+          <t xml:space="preserve">accepted.bold.composed[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…引き留める、か。…まあ、悪くない判断だね</t>
+          <t xml:space="preserve">…もっと大きい舞台で証明するよ。…見ててね</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.composed[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.bold.composed[1]</t>
+          <t xml:space="preserve">accepted.bold.composed[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3013,14 +3013,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…信じてくれるなら。…もう少し付き合うよ</t>
+          <t xml:space="preserve">…行かせてもらう。世話になったね</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.composed[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.bold.composed[1]</t>
+          <t xml:space="preserve">defended.bold.composed[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3045,14 +3045,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後にもう一度、か。…悪くないね</t>
+          <t xml:space="preserve">…そこまで言うなら、残るよ</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.composed[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.bold.composed[1]</t>
+          <t xml:space="preserve">defended.bold.composed[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3077,14 +3077,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、いいよ。…潮時だし</t>
+          <t xml:space="preserve">…簡単には手放さない、か。…悪い気はしないね</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.composed[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.bold.composed[1]</t>
+          <t xml:space="preserve">defense_failed.bold.composed[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんな終わり方、か。…まあ、いいよ</t>
+          <t xml:space="preserve">…ごめんね。…でも、決意は固いんだ</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.composed[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold.composed[1]</t>
+          <t xml:space="preserve">defense_failed.bold.composed[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3141,14 +3141,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん、限界か。…認めるよ</t>
+          <t xml:space="preserve">…止めても止まらないよ。じゃあね</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.bold.composed[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.bold.composed[1]</t>
+          <t xml:space="preserve">default.bold.composed[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3173,14 +3173,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…結果が全て、か。…そうだね</t>
+          <t xml:space="preserve">…まだ終わりじゃないよ。…やってみせる</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.composed[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold.composed[1]</t>
+          <t xml:space="preserve">former_champ.bold.composed[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3205,14 +3205,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。…王者に引退を勧める、か。…早いよ</t>
+          <t xml:space="preserve">…もう一シーズンだけ。…結果は出すよ</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.bold.composed[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.bold.composed[1]</t>
+          <t xml:space="preserve">heel.bold.composed[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3237,14 +3237,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん、邪魔か。…はっきり言ってくれるね</t>
+          <t xml:space="preserve">…引き留める、か。…まあ、悪くない判断だね</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.composed[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.bold.composed[1]</t>
+          <t xml:space="preserve">high_trust.bold.composed[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3269,14 +3269,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…諦めるのはまだ早いよ。…見ていて</t>
+          <t xml:space="preserve">…信じてくれるなら。…もう少し付き合うよ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.composed[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.bold.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.bold.composed[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3301,14 +3301,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。…私がいなくなったら困るのは、そっちだよ</t>
+          <t xml:space="preserve">…最後にもう一度、か。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.composed[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold.composed[1]</t>
+          <t xml:space="preserve">accept_heel.bold.composed[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3333,14 +3333,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…背負い切った。…まあ、上出来でしょ</t>
+          <t xml:space="preserve">…まあ、いいよ。…潮時だし</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.composed[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.bold.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.bold.composed[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3365,14 +3365,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げなかった。…それだけで十分かな</t>
+          <t xml:space="preserve">…こんな終わり方、か。…まあ、いいよ</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.composed[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.bold.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.bold.composed[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3397,14 +3397,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嫌われ者か。…悪くない肩書だったよ</t>
+          <t xml:space="preserve">…ふぅん、限界か。…認めるよ</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.composed[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.bold.composed[1]</t>
+          <t xml:space="preserve">accept_winless.bold.composed[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3429,14 +3429,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あっという間だったね。…悪くなかったよ</t>
+          <t xml:space="preserve">…結果が全て、か。…そうだね</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.composed[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.bold.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.bold.composed[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3461,14 +3461,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嘘だろ。…まだ、始まったばかりなのに</t>
+          <t xml:space="preserve">…ふぅん。…王者に引退を勧める、か。…早いよ</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.composed[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.bold.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.bold.composed[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3493,14 +3493,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだやれると思ってた。…参ったな</t>
+          <t xml:space="preserve">…ふぅん、邪魔か。…はっきり言ってくれるね</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.composed[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.bold.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.bold.composed[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3525,14 +3525,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は限界か。…でもまあ、やりきったよ</t>
+          <t xml:space="preserve">…諦めるのはまだ早いよ。…見ていて</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.composed[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.bold.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.bold.composed[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンのまま終わりか。…皮肉だね</t>
+          <t xml:space="preserve">…ふぅん。…私がいなくなったら困るのは、そっちだよ</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.composed[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">A1_champion.bold.composed[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行く理由がないね。ここで続けるよ</t>
+          <t xml:space="preserve">…背負い切った。…まあ、上出来でしょ</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.composed[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.bold.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.bold.composed[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。まあ…分かってくれるなら、それでいい。やるよ。</t>
+          <t xml:space="preserve">…逃げなかった。…それだけで十分かな</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.composed[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3638,29 +3638,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.bold.composed[1]</t>
+          <t xml:space="preserve">A3_heel.bold.composed[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ゼロじゃないなら…まあ、いいよ。次はもう少し期待してる。</t>
+          <t xml:space="preserve">…嫌われ者か。…悪くない肩書だったよ</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.composed[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3670,29 +3670,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.bold.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.bold.composed[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。まあいいけど…次は、ないよ。覚えておいて。</t>
+          <t xml:space="preserve">…あっという間だったね。…悪くなかったよ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.composed[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3702,29 +3702,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold.composed[1]</t>
+          <t xml:space="preserve">B1_young.bold.composed[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。{tenure}率直に言うね。{record}この額は…ちょっと寂しいかな。</t>
+          <t xml:space="preserve">…嘘だろ。…まだ、始まったばかりなのに</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.composed[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3734,29 +3734,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.bold.composed[1]</t>
+          <t xml:space="preserve">B2_prime.bold.composed[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。…まあいいよ。ただ…我慢にも限度がある。それだけ。</t>
+          <t xml:space="preserve">…まだやれると思ってた。…参ったな</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.composed[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3766,29 +3766,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold.composed[1]</t>
+          <t xml:space="preserve">B3_older.bold.composed[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。{tenure}決めたよ。…出る。特に未練はない。</t>
+          <t xml:space="preserve">…体は限界か。…でもまあ、やりきったよ</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.composed[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3798,29 +3798,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.bold.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.bold.composed[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪いけど、もう決めた。…変わらないよ。</t>
+          <t xml:space="preserve">…チャンピオンのまま終わりか。…皮肉だね</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.composed[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3830,544 +3830,544 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまで言うなら…まあ、もう少し付き合うよ。</t>
+          <t xml:space="preserve">…行く理由がないね。ここで続けるよ</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_accept.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…なるほど。まあ…分かってくれるなら、それでいい。やるよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_accept.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ゼロじゃないなら…まあ、いいよ。次はもう少し期待してる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_refuse.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ふぅん。まあいいけど…次は、ないよ。覚えておいて。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_open.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長。{tenure}率直に言うね。{record}この額は…ちょっと寂しいかな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そう。…まあいいよ。ただ…我慢にも限度がある。それだけ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。…もう無理だよ。お世話になりました…とは、正直言えないかな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もう決めた。ここにいる理由が、なくなったから。…じゃあね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…もっと上で闘いたい。ここじゃ、物足りなくてね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長。{tenure}決めたよ。…出る。特に未練はない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まあ、そうなるだろうとは思ってた。{rivalry}…じゃあね、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悪いけど、もう決めた。…変わらないよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そこまで言うなら…まあ、もう少し付き合うよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.bold.composed[1]</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr" s="2">
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr" s="12">
+      <c r="D123" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.bold.composed[1]</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr" s="2">
+      <c r="E123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr" s="3">
+      <c r="F123" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…悪いけど、ここを離れる気はないよ。
 今の仲間がいるから</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="40" customHeight="1">
-      <c r="A112" t="inlineStr" s="15">
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.bold.composed[1]</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr" s="2">
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr" s="12">
+      <c r="D124" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.bold.composed[1]</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr" s="2">
+      <c r="E124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr" s="3">
+      <c r="F124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…ここが居場所だから。
 悪いね</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="40" customHeight="1">
-      <c r="A113" t="inlineStr" s="15">
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.bold.composed[1]</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr" s="2">
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr" s="12">
+      <c r="D125" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.bold.composed[1]</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr" s="2">
+      <c r="E125" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr" s="3">
+      <c r="F125" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…引き抜き？ …面白いね。条件を聞こうか</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="40" customHeight="1">
-      <c r="A114" t="inlineStr" s="15">
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.bold.composed[1]</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr" s="2">
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr" s="12">
+      <c r="D126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.bold.composed[1]</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr" s="2">
+      <c r="E126" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr" s="3">
+      <c r="F126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…いいよ、行く。
 実力で示すだけだ</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="40" customHeight="1">
-      <c r="A115" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのメンバーに、もう少し目を配っていただけませんか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="40" customHeight="1">
-      <c r="A116" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次のメインカード、私たちで組ませてください。今ならハマります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="40" customHeight="1">
-      <c r="A117" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの給与、一度見直しの俎上に乗せてもらえませんか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="40" customHeight="1">
-      <c r="A118" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちが積み上げてきたもの、評価の俎上に乗っていますか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="40" customHeight="1">
-      <c r="A119" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、ありがとうございます。その言葉、胸に留めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="40" customHeight="1">
-      <c r="A121" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく受け取ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ありがたく頂戴します。期待は超えてみせます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。次の機会を待ちます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。お預かりします。</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、ありがとうございます。気持ちが引き締まります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…承知しました。次の機会に、また話します。</t>
-        </is>
-      </c>
-    </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.bold[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.bold[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4392,14 +4392,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういうご配慮ですか。ありがたく頂戴します。</t>
+          <t xml:space="preserve">社長、私たちのメンバーに、もう少し目を配っていただけませんか。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.bold[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.bold[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4424,14 +4424,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。その言葉、励みにします。</t>
+          <t xml:space="preserve">社長、次のメインカード、私たちで組ませてください。今ならハマります。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.bold[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.bold[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4456,14 +4456,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。</t>
+          <t xml:space="preserve">社長、私たちの給与、一度見直しの俎上に乗せてもらえませんか。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.bold[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.bold[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4488,14 +4488,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく受け取ります。</t>
+          <t xml:space="preserve">社長、私たちが積み上げてきたもの、評価の俎上に乗っていますか。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4520,14 +4520,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました、次は声をかけます。</t>
+          <t xml:space="preserve">社長、ありがとうございます。その言葉、胸に留めます。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4552,14 +4552,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも、大事ですから。</t>
+          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4584,14 +4584,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました、注意します。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4616,14 +4616,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">ありがたく頂戴します。期待は超えてみせます。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4648,14 +4648,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。営業に響くなら線を引きます。</t>
+          <t xml:space="preserve">…承知しました。次の機会を待ちます。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4680,14 +4680,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。お預かりします。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4712,14 +4712,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご迷惑をおかけしました。明日から、しっかり出ます。</t>
+          <t xml:space="preserve">社長、ありがとうございます。気持ちが引き締まります。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4744,14 +4744,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。次は、しっかりやります。</t>
+          <t xml:space="preserve">…承知しました。次の機会に、また話します。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4776,14 +4776,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく頂戴します。</t>
+          <t xml:space="preserve">…なるほど、そういうご配慮ですか。ありがたく頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4808,14 +4808,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。少し、休ませてもらいます。</t>
+          <t xml:space="preserve">ありがとうございます。その言葉、励みにします。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4840,14 +4840,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫です。まだ、いけます。</t>
+          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4872,14 +4872,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、メンバーケアですか。私も助かります。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく受け取ります。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4904,14 +4904,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。私からメンバーに話します。</t>
+          <t xml:space="preserve">…承知しました、次は声をかけます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4936,14 +4936,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。穏便に収めます。</t>
+          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも、大事ですから。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4968,14 +4968,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮ありがとうございます。下の子のフォロー、助かります。</t>
+          <t xml:space="preserve">…承知しました、注意します。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5000,14 +5000,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。態度、改めます。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5032,14 +5032,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（小さく頷いて、それ以上は語らなかった）</t>
+          <t xml:space="preserve">…承知しました。営業に響くなら線を引きます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5064,14 +5064,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがたく頂戴します。</t>
+          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5096,14 +5096,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。怪我させては元も子もないですね。緩めます。</t>
+          <t xml:space="preserve">…ご迷惑をおかけしました。明日から、しっかり出ます。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5128,14 +5128,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。このまま続けます。</t>
+          <t xml:space="preserve">…ありがとうございます。次は、しっかりやります。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5160,14 +5160,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、下の子のケアですか。ありがたく頂戴します。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5192,14 +5192,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、同じ場所には立てない</t>
+          <t xml:space="preserve">…ありがとうございます。少し、休ませてもらいます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5224,14 +5224,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等。受けて立とう</t>
+          <t xml:space="preserve">…大丈夫です。まだ、いけます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5241,29 +5241,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、まだ先がある。ここからだよ</t>
+          <t xml:space="preserve">…なるほど、メンバーケアですか。私も助かります。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5273,29 +5273,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…なるほど。…これが、その先か——）</t>
+          <t xml:space="preserve">…承知しました。私からメンバーに話します。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…天井か。…でもまあ、ここまで来たんだし上出来だよ</t>
+          <t xml:space="preserve">…ありがとうございます。穏便に収めます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5337,29 +5337,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂が見えてきた。もうひと踏ん張り、かな</t>
+          <t xml:space="preserve">…ご配慮ありがとうございます。下の子のフォロー、助かります。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5369,29 +5369,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…通過点、だね。まだ先がある</t>
+          <t xml:space="preserve">…承知しました。態度、改めます。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5401,29 +5401,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。なかなかの景色じゃない</t>
+          <t xml:space="preserve">（小さく頷いて、それ以上は語らなかった）</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5433,29 +5433,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、当然っちゃ当然かな</t>
+          <t xml:space="preserve">…ご配慮、ありがたく頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5465,29 +5465,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、みんなが見てるなら、格好つけないとね</t>
+          <t xml:space="preserve">…承知しました。怪我させては元も子もないですね。緩めます。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5497,29 +5497,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えない。…こういうこともあるか</t>
+          <t xml:space="preserve">…ありがとうございます。このまま続けます。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5529,29 +5529,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…目が覚めた。…ここで終わるのは、つまらないね</t>
+          <t xml:space="preserve">…なるほど、下の子のケアですか。ありがたく頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.composed</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5561,29 +5561,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">bold.attack.composed</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…待たせたね。…ここからだよ</t>
+          <t xml:space="preserve">もう、同じ場所には立てない</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.composed[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.composed</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5593,29 +5593,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold.composed[1]</t>
+          <t xml:space="preserve">bold.defend.composed</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなはずじゃないんだけど。…焦ってはいないよ</t>
+          <t xml:space="preserve">上等。受けて立とう</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5640,14 +5640,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…治ったはず、なんだけどね。…もたついてる</t>
+          <t xml:space="preserve">…ま、まだ先がある。ここからだよ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5672,14 +5672,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…怯えてる？ …まさかね。…まさか</t>
+          <t xml:space="preserve">（…なるほど。…これが、その先か——）</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.composed[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.bold.composed[1]</t>
+          <t xml:space="preserve">cap_reached.bold.composed[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5704,14 +5704,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は大丈夫。…気持ちだけが、まだ追いつかない</t>
+          <t xml:space="preserve">…天井か。…でもまあ、ここまで来たんだし上出来だよ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.composed[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5721,29 +5721,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.bold.composed[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい試合だった。出し惜しみなんてできなかったよ</t>
+          <t xml:space="preserve">…頂が見えてきた。もうひと踏ん張り、かな</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.composed[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5753,29 +5753,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.bold.composed[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが頂点。渡す気はないよ</t>
+          <t xml:space="preserve">…通過点、だね。まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.composed[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5785,29 +5785,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.bold.composed[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全部やりきった。悔いはないよ</t>
+          <t xml:space="preserve">…ふぅん。なかなかの景色じゃない</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.bold.composed[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5817,29 +5817,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.bold.composed[1]</t>
+          <t xml:space="preserve">pop_growth.bold.composed[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…リングの外でも、やるべきことをやっただけだよ</t>
+          <t xml:space="preserve">…ま、当然っちゃ当然かな</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.composed[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5849,29 +5849,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold.composed[1]</t>
+          <t xml:space="preserve">pop_star.bold.composed[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、結果は出したからね。…でもまだ先がある</t>
+          <t xml:space="preserve">…ま、みんなが見てるなら、格好つけないとね</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.bold.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5881,29 +5881,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…通過点だね。次を見てなよ</t>
+          <t xml:space="preserve">…燃えない。…こういうこともあるか</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
@@ -5923,19 +5923,19 @@
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム。燃える。それだけだ</t>
+          <t xml:space="preserve">…目が覚めた。…ここで終わるのは、つまらないね</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5945,29 +5945,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことは分かってる。全力でぶつかる</t>
+          <t xml:space="preserve">…待たせたね。…ここからだよ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.composed[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.composed[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5977,29 +5977,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[3]</t>
+          <t xml:space="preserve">defeat.bold.composed[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この闘志、ドームで解き放つ</t>
+          <t xml:space="preserve">…こんなはずじゃないんだけど。…焦ってはいないよ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.composed[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6009,29 +6009,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.bold.composed[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。…達成感しかない</t>
+          <t xml:space="preserve">…治ったはず、なんだけどね。…もたついてる</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.composed[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6041,29 +6041,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">injury_severe_recovery.bold.composed[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でやった。それが報われた</t>
+          <t xml:space="preserve">…怯えてる？ …まさかね。…まさか</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.composed[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.composed[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6073,29 +6073,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[3]</t>
+          <t xml:space="preserve">penalty_end.bold.composed[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと上を目指す</t>
+          <t xml:space="preserve">…体は大丈夫。…気持ちだけが、まだ追いつかない</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.composed[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6105,29 +6105,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.bold.composed[1]</t>
+          <t xml:space="preserve">bestMatch.bold.composed[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ先がある。焦らず行くよ</t>
+          <t xml:space="preserve">…いい試合だった。出し惜しみなんてできなかったよ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.bold.composed[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6137,29 +6137,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.bold.composed[1]</t>
+          <t xml:space="preserve">champion.bold.composed[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないチームだよ。居心地がいい</t>
+          <t xml:space="preserve">…ここが頂点。渡す気はないよ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.composed[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6169,29 +6169,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.bold.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.bold.composed[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この程度なら大丈夫。慌てないで</t>
+          <t xml:space="preserve">…全部やりきった。悔いはないよ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.bold.composed[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6201,29 +6201,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.bold.composed[1]</t>
+          <t xml:space="preserve">mediaAward.bold.composed[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないね。この期待に応えるだけだよ</t>
+          <t xml:space="preserve">…リングの外でも、やるべきことをやっただけだよ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.bold.composed[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6233,29 +6233,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.bold.composed[1]</t>
+          <t xml:space="preserve">mvp.bold.composed[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいる意味、少し考え直してもいいかな</t>
+          <t xml:space="preserve">…まあ、結果は出したからね。…でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.bold.composed[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6265,29 +6265,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.bold.composed[1]</t>
+          <t xml:space="preserve">rookie.bold.composed[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、少し立ち止まってるだけだよ。…たぶん</t>
+          <t xml:space="preserve">…通過点だね。次を見てなよ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.bold.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6297,29 +6297,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ先がある。…ここでなら</t>
+          <t xml:space="preserve">ドーム。燃える。それだけだ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.bold.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.composed[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6329,29 +6329,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。…まあ、いいけど</t>
+          <t xml:space="preserve">…やるべきことは分かってる。全力でぶつかる</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.bold.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.composed[3]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6361,29 +6361,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[3]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるね。…でも、まだ負けるつもりはない</t>
+          <t xml:space="preserve">この闘志、ドームで解き放つ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.bold.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6393,29 +6393,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。…まだ順番が来ないか</t>
+          <t xml:space="preserve">満員。…達成感しかない</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.bold.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.composed[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…使ってくれないと、困るんだけど</t>
+          <t xml:space="preserve">全力でやった。それが報われた</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.bold.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.composed[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6457,29 +6457,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、いいんだけどね。一人でも</t>
+          <t xml:space="preserve">次はもっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.composed[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.bold.composed[1]</t>
+          <t xml:space="preserve">N1.bold.composed[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6504,14 +6504,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くんだ。…まあ、{name2}が決めたことだからね</t>
+          <t xml:space="preserve">…まだ先がある。焦らず行くよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.composed[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.bold.composed[1]</t>
+          <t xml:space="preserve">N2.bold.composed[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6536,14 +6536,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…でも、まだだね</t>
+          <t xml:space="preserve">…悪くないチームだよ。居心地がいい</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.composed[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6553,12 +6553,12 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.bold.composed[1]</t>
+          <t xml:space="preserve">N3.bold.composed[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6568,14 +6568,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は返す。…覚えておいて</t>
+          <t xml:space="preserve">…この程度なら大丈夫。慌てないで</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.composed[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.bold.composed[1]</t>
+          <t xml:space="preserve">N4.bold.composed[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6600,14 +6600,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…うちの看板、守れたかな</t>
+          <t xml:space="preserve">…悪くないね。この期待に応えるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.composed[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6617,29 +6617,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.bold.composed[1]</t>
+          <t xml:space="preserve">N5_low.bold.composed[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。結果で返すよ</t>
+          <t xml:space="preserve">…ここにいる意味、少し考え直してもいいかな</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.composed[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6649,29 +6649,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.bold.composed[1]</t>
+          <t xml:space="preserve">N5_warning.bold.composed[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。しっかり追い込むよ</t>
+          <t xml:space="preserve">…ま、少し立ち止まってるだけだよ。…たぶん</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6681,29 +6681,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.bold.composed[1]</t>
+          <t xml:space="preserve">breakthrough.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…信じてくれるなら、応えないとね</t>
+          <t xml:space="preserve">…まだ先がある。…ここでなら</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6713,29 +6713,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.bold.composed[1]</t>
+          <t xml:space="preserve">G1.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ終わってないよ。やるだけやる</t>
+          <t xml:space="preserve">…ふぅん。…まあ、いいけど</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6745,29 +6745,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.bold.composed[1]</t>
+          <t xml:space="preserve">G2.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。任せて</t>
+          <t xml:space="preserve">…やるね。…でも、まだ負けるつもりはない</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6777,29 +6777,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.bold.composed[1]</t>
+          <t xml:space="preserve">G3.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい雰囲気だね。こういうのも大事だよ</t>
+          <t xml:space="preserve">…ふぅん。…まだ順番が来ないか</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6809,29 +6809,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.bold.composed[1]</t>
+          <t xml:space="preserve">G4.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…充電してくるよ。戻ったらまた行こう</t>
+          <t xml:space="preserve">…使ってくれないと、困るんだけど</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6841,29 +6841,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.bold.composed[1]</t>
+          <t xml:space="preserve">R2.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…早く戻るよ。ありがとう</t>
+          <t xml:space="preserve">…まあ、いいんだけどね。一人でも</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.bold.composed[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6873,29 +6873,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.bold.composed[1]</t>
+          <t xml:space="preserve">R3.modal.bold.composed[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。無駄にはしないよ</t>
+          <t xml:space="preserve">…行くんだ。…まあ、{name2}が決めたことだからね</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6905,29 +6905,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold.composed[1]</t>
+          <t xml:space="preserve">R4.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないね。いつも通りやるよ</t>
+          <t xml:space="preserve">…勝った。…でも、まだだね</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6937,29 +6937,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.bold.composed[1]</t>
+          <t xml:space="preserve">R5.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない条件なんだよね。…少し考えてもいいかな</t>
+          <t xml:space="preserve">…次は返す。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6969,29 +6969,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.bold.composed[1]</t>
+          <t xml:space="preserve">warVictory.voice.bold.composed[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルト、狙わせてもらうよ。組んでくれる？</t>
+          <t xml:space="preserve">…勝った。…うちの看板、守れたかな</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.composed[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.bold.composed[1]</t>
+          <t xml:space="preserve">bonus.bold.composed[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7016,14 +7016,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決着をつけたいんだ。組んでくれないかな</t>
+          <t xml:space="preserve">…ありがとう。結果で返すよ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.composed[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.bold.composed[1]</t>
+          <t xml:space="preserve">camp.bold.composed[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7048,14 +7048,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が限界みたいだ。少し休むよ</t>
+          <t xml:space="preserve">…いい機会だね。しっかり追い込むよ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.composed[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.bold.composed[1]</t>
+          <t xml:space="preserve">encourage_high_trust.bold.composed[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7080,14 +7080,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままだと先がないよ。考え直してくれないかな</t>
+          <t xml:space="preserve">…信じてくれるなら、応えないとね</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.composed[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7097,12 +7097,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.bold.composed[1]</t>
+          <t xml:space="preserve">encourage.bold.composed[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7112,14 +7112,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し上に行きたい。特訓させてくれないかな</t>
+          <t xml:space="preserve">…まだ終わってないよ。やるだけやる</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold.composed[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.bold.composed[1]</t>
+          <t xml:space="preserve">faction_decree.bold.composed[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩に伝えておきたいことがあるんだ。任せてくれないかな</t>
+          <t xml:space="preserve">……納得はしていない。それだけは言っておくよ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.composed[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.bold.composed[1]</t>
+          <t xml:space="preserve">media.bold.composed[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7176,14 +7176,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、こういうこともあるよ。少し待ってて</t>
+          <t xml:space="preserve">…いい機会だね。任せて</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.composed[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.bold.composed[1]</t>
+          <t xml:space="preserve">party.bold.composed[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7208,14 +7208,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪いけど、あの人とはちょっと厳しいかな</t>
+          <t xml:space="preserve">…いい雰囲気だね。こういうのも大事だよ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.composed[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7225,12 +7225,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.bold.composed[1]</t>
+          <t xml:space="preserve">refresh_leave.bold.composed[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7240,14 +7240,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私は私のやり方を変えるつもりはないよ。それだけ</t>
+          <t xml:space="preserve">…充電してくるよ。戻ったらまた行こう</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold.composed[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.bold.composed[1]</t>
+          <t xml:space="preserve">special_treatment.bold.composed[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7272,14 +7272,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない組み合わせだね。いいものにしよう</t>
+          <t xml:space="preserve">…早く戻るよ。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.composed[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.bold.composed[1]</t>
+          <t xml:space="preserve">trainer.bold.composed[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7304,14 +7304,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全国か。いい機会だね、自分のペースでやるよ</t>
+          <t xml:space="preserve">…いい機会だね。無駄にはしないよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.composed[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.bold.composed[1]</t>
+          <t xml:space="preserve">E1.bold.composed[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7336,14 +7336,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…撮られるのは嫌いじゃないよ。いい写真にしよう</t>
+          <t xml:space="preserve">…悪くないね。いつも通りやるよ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.composed[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.bold.composed[1]</t>
+          <t xml:space="preserve">E6.bold.composed[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7368,14 +7368,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、自分のペースで話せばいいんでしょ。大丈夫</t>
+          <t xml:space="preserve">…悪くない条件なんだよね。…少し考えてもいいかな</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.composed[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.bold.composed[1]</t>
+          <t xml:space="preserve">S_boycott.bold.composed[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7400,14 +7400,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。自分らしくやらせてもらうよ</t>
+          <t xml:space="preserve">…出してもらえないのに、練習する意味あるのかな</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.composed[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7417,29 +7417,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">S_boycott.bold.composed[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
+          <t xml:space="preserve">…リングに上がれないなら、同じことだよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.bold.composed[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7449,29 +7449,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">S_grumble.bold.composed[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">（「…この扱いは、さすがに通らないよ」と静かに言い切り、場が凍りついた）</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.bold.composed[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7481,29 +7481,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">S_sns.bold.composed[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待には応える。見ててくれ</t>
+          <t xml:space="preserve">（SNSに「…このまま終わるつもりはないよ」と静かな宣言を投稿）</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.composed[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7513,29 +7513,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">S1.bold.composed[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">…ベルト、狙わせてもらうよ。組んでくれる？</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.composed[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7545,29 +7545,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">S2.bold.composed[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点まで。…見ていて</t>
+          <t xml:space="preserve">…決着をつけたいんだ。組んでくれないかな</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.composed[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7577,29 +7577,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">S3.bold.composed[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
+          <t xml:space="preserve">…体が限界みたいだ。少し休むよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.composed[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7609,29 +7609,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">S4_direct.bold.composed[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…問題ない。少し休めば治る</t>
+          <t xml:space="preserve">…このままだと先がないよ。考え直してくれないかな</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.bold.composed[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7641,29 +7641,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold.composed[1]</t>
+          <t xml:space="preserve">S4_silent.bold.composed[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
+          <t xml:space="preserve">…………（拳を握り、それから静かに息を吐いた）</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.composed[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7673,29 +7673,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.composed[1]</t>
+          <t xml:space="preserve">S5.bold.composed[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">…もう少し上に行きたい。特訓させてくれないかな</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.composed[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7705,29 +7705,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.composed[2]</t>
+          <t xml:space="preserve">S6.bold.composed[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待には応える。見ててくれ</t>
+          <t xml:space="preserve">…後輩に伝えておきたいことがあるんだ。任せてくれないかな</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.composed[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7737,29 +7737,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold.composed[1]</t>
+          <t xml:space="preserve">B1.bold.composed[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">…まあ、こういうこともあるよ。少し待ってて</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.composed[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7769,29 +7769,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.bold.composed[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点まで。…見ていて</t>
+          <t xml:space="preserve">…悪いけど、あの人とはちょっと厳しいかな</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.composed[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7801,29 +7801,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.bold.composed[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
+          <t xml:space="preserve">…私は私のやり方を変えるつもりはないよ。それだけ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.composed[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7833,29 +7833,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.composed[2]</t>
+          <t xml:space="preserve">B4_brand.bold.composed[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…問題ない。少し休めば治る</t>
+          <t xml:space="preserve">…悪くない組み合わせだね。いいものにしよう</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.composed[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7865,29 +7865,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.composed[1]</t>
+          <t xml:space="preserve">B4_cm.bold.composed[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
+          <t xml:space="preserve">…全国か。いい機会だね、自分のペースでやるよ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.composed[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7897,29 +7897,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.composed[2]</t>
+          <t xml:space="preserve">B4_fan.bold.composed[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
+          <t xml:space="preserve">…最高の思い出を持って帰ってもらおうか</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.composed[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7929,29 +7929,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold.composed[1]</t>
+          <t xml:space="preserve">B4_fan.bold.composed[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
+          <t xml:space="preserve">…全員笑顔で帰す。…それが私の仕事だからね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.composed[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7961,29 +7961,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.bold.composed[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
+          <t xml:space="preserve">…ランウェイも私の舞台だよ。…全部持っていく</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.composed[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7993,29 +7993,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.bold.composed[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
+          <t xml:space="preserve">…プロレスもファッションも。…どっちも私のものだね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.composed[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8025,29 +8025,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.bold.composed[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…取り返す。…覚えておいて</t>
+          <t xml:space="preserve">…撮られるのは嫌いじゃないよ。いい写真にしよう</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.composed[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8057,29 +8057,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold.composed[1]</t>
+          <t xml:space="preserve">B4_variety.bold.composed[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
+          <t xml:space="preserve">…まあ、自分のペースで話せばいいんでしょ。大丈夫</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.composed[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8089,29 +8089,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">B4.bold.composed[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
+          <t xml:space="preserve">…いい機会だね。自分らしくやらせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8136,14 +8136,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
@@ -8168,14 +8168,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.composed[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8200,14 +8200,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
+          <t xml:space="preserve">…期待には応える。見ててくれ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
@@ -8232,14 +8232,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
@@ -8264,14 +8264,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…取り返す。…覚えておいて</t>
+          <t xml:space="preserve">…頂点まで。…見ていて</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
@@ -8296,14 +8296,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
+          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.bold.composed[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8313,29 +8313,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[2]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無理なものは無理。…それだけ</t>
+          <t xml:space="preserve">…問題ない。少し休めば治る</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.bold.composed[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8345,29 +8345,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.bold.composed[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…壁作ってない？ …まあ、いいけど</t>
+          <t xml:space="preserve">…片付いた相手だよ。…なのに、まだ目で追ってる</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.bold.composed[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8377,29 +8377,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.bold.composed[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なかなかやるね。認めてあげてもいいかな</t>
+          <t xml:space="preserve">…終わった話らしいね。…じゃあ、この重さは何なんだろう</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.composed[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8409,29 +8409,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.composed[1]</t>
+          <t xml:space="preserve">draftInterest.bold.composed[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の相棒だね。…二人なら怖いものはない</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.composed[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8441,29 +8441,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.composed[1]</t>
+          <t xml:space="preserve">draftJoin.bold.composed[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった。…次に行くよ</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.composed[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8473,29 +8473,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.composed[1]</t>
+          <t xml:space="preserve">draftJoin.bold.composed[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…面白い相手だね。…超えてみせるよ</t>
+          <t xml:space="preserve">…期待には応える。見ててくれ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold.composed[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8505,29 +8505,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.composed[1]</t>
+          <t xml:space="preserve">faGreeting.bold.composed[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の敵だね。…超える。それだけ</t>
+          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.composed[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8537,29 +8537,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.composed[1]</t>
+          <t xml:space="preserve">faSigning.bold.composed[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…生涯の勝負だ。…望むところ</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.composed[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8569,29 +8569,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.composed[1]</t>
+          <t xml:space="preserve">faWelcome.bold.composed[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが最高の場所だ。…もっと強くしてみせる</t>
+          <t xml:space="preserve">…頂点まで。…見ていて</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.composed[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8601,29 +8601,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.composed[1]</t>
+          <t xml:space="preserve">injury.bold.composed[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう付き合いきれないかな。…覚えておいて</t>
+          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.composed[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8633,29 +8633,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.composed[1]</t>
+          <t xml:space="preserve">injury.bold.composed[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この扱いは、ちょっとどうかと思うけど</t>
+          <t xml:space="preserve">…問題ない。少し休めば治る</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.composed[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8665,29 +8665,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">release.bold.composed[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻ったね。…あの感覚は覚えた</t>
+          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.composed[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8697,29 +8697,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.composed[1]</t>
+          <t xml:space="preserve">release.bold.composed[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は重い。でも、最後の舞台を降りる理由にはならないよ</t>
+          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.composed[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8729,29 +8729,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.composed[2]</t>
+          <t xml:space="preserve">rentalGreeting.bold.composed[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た者だけが立てる場所だ。…受けて立つ</t>
+          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold.composed[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8761,29 +8761,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.composed[1]</t>
+          <t xml:space="preserve">scoutGreeting.bold.composed[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰でも、受けて立つよ。慌てる場面じゃない</t>
+          <t xml:space="preserve">…目は確かみたいだね。まぁ…頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.composed[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8793,29 +8793,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.composed[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.bold.composed[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人でも並びなよ。…上等。並んだだけ、倒すから</t>
+          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.composed[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8825,29 +8825,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.composed[1]</t>
+          <t xml:space="preserve">titleDefense.bold.composed[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人片づけたよ。息は上がってるけど、退く場面じゃない。次、来なよ</t>
+          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.composed[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8857,29 +8857,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.composed[2]</t>
+          <t xml:space="preserve">titleLoss.bold.composed[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ拳は握れる。…このリングは渡さないよ。次は誰だ</t>
+          <t xml:space="preserve">…取り返す。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.composed[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8889,29 +8889,29 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.composed[1]</t>
+          <t xml:space="preserve">titleWin.bold.composed[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人が揃えば……どの団体にも、負ける道理はなかった</t>
+          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8921,29 +8921,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.composed[2]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最強の三人だった。異論があるなら、またこのリングで証明しよう</t>
+          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.composed[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8953,29 +8953,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞は受け取ろう。だが……次は旗ごともらいに行く。覚えておけ</t>
+          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8985,29 +8985,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.composed[2]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で満足する性分ではない。次は、全てを攫う</t>
+          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9017,29 +9017,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ようと……立っている者が、最後に語る権利を得る。今日はそれだけのこと</t>
+          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9049,29 +9049,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.composed[2]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。だが、拳を下ろす理由がどこにもなかった</t>
+          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9081,29 +9081,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝。…まあ、当然かな</t>
+          <t xml:space="preserve">…取り返す。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9113,29 +9113,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。…でも、次は違う</t>
+          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9145,29 +9145,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然だね。…次も同じ</t>
+          <t xml:space="preserve">…無理なものは無理。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9177,29 +9177,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ上がある。…次は獲る</t>
+          <t xml:space="preserve">…壁作ってない？ …まあ、いいけど</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9209,29 +9209,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後の一戦。…獲りにいくよ</t>
+          <t xml:space="preserve">…なかなかやるね。認めてあげてもいいかな</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9241,29 +9241,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝つよ。…それだけ</t>
+          <t xml:space="preserve">…最高の相棒だね。…二人なら怖いものはない</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9273,29 +9273,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選ばれたか。…まあ、当然だろうね</t>
+          <t xml:space="preserve">…終わった。…次に行くよ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9305,29 +9305,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…手加減はしない。…覚悟して</t>
+          <t xml:space="preserve">…面白い相手だね。…超えてみせるよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9337,29 +9337,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…獲った。…ここが頂点か。…悪くないね</t>
+          <t xml:space="preserve">…最高の敵だね。…超える。それだけ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9369,29 +9369,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…格の違い、見せてあげるよ</t>
+          <t xml:space="preserve">…生涯の勝負だ。…望むところ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.composed[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9401,29 +9401,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.composed[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…手加減はしない。覚悟してね</t>
+          <t xml:space="preserve">…ここが最高の場所だ。…もっと強くしてみせる</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.composed[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9433,29 +9433,29 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.composed[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるか。…まあ、賢い判断かもね</t>
+          <t xml:space="preserve">…もう付き合いきれないかな。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.composed[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9465,29 +9465,29 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.composed[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.composed[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けた。…でも、次はこうはいかないよ</t>
+          <t xml:space="preserve">…この扱いは、ちょっとどうかと思うけど</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.composed[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9497,29 +9497,29 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.composed[1]</t>
+          <t xml:space="preserve">bold.composed[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だよ。…もう少し手応えが欲しかったけどね</t>
+          <t xml:space="preserve">…戻ったね。…あの感覚は覚えた</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.composed[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">preFinal.bold.composed[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9544,14 +9544,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だよ。…うちを甘く見ないでね</t>
+          <t xml:space="preserve">…身体は重い。でも、最後の舞台を降りる理由にはならないよ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.composed[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">preFinal.bold.composed[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9576,44 +9576,940 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなもんかな。…まだまだ行けるよ</t>
+          <t xml:space="preserve">ここまで来た者だけが立てる場所だ。…受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手が誰でも、受けて立つよ。慌てる場面じゃない</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人でも並びなよ。…上等。並んだだけ、倒すから</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一人片づけたよ。息は上がってるけど、退く場面じゃない。次、来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ拳は握れる。…このリングは渡さないよ。次は誰だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三人が揃えば……どの団体にも、負ける道理はなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最強の三人だった。異論があるなら、またこのリングで証明しよう</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">賞は受け取ろう。だが……次は旗ごともらいに行く。覚えておけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この程度で満足する性分ではない。次は、全てを攫う</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人来ようと……立っている者が、最後に語る権利を得る。今日はそれだけのこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">身体は重い。だが、拳を下ろす理由がどこにもなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…優勝。…まあ、当然かな</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悔しいね。…でも、次は違う</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…当然だね。…次も同じ</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まだ上がある。…次は獲る</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…最後の一戦。…獲りにいくよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…勝つよ。…それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…選ばれたか。…まあ、当然だろうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…手加減はしない。…覚悟して</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…獲った。…ここが頂点か。…悪くないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…格の違い、見せてあげるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…手加減はしない。覚悟してね</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるか。…まあ、賢い判断かもね</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けた。…でも、次はこうはいかないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…当然の結果だよ。…もう少し手応えが欲しかったけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…当然の結果だよ。…うちを甘く見ないでね</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.composed[2]</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…こんなもんかな。…まだまだ行けるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.bold.composed[1]</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr" s="2">
+      <c r="B316" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr" s="12">
+      <c r="D316" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.bold.composed[1]</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr" s="2">
+      <c r="E316" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr" s="3">
+      <c r="F316" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…頂点か。…でもまだ先がある気がするね</t>
         </is>
       </c>
     </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.composed[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…目は確かみたいだね。まぁ…頑張るよ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H290"/>
+  <autoFilter ref="A1:H318"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
@@ -364,7 +364,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.bold[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -379,7 +379,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.composed[1]</t>
+          <t xml:space="preserve">atk.composed.bold[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -396,7 +396,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.bold[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -411,7 +411,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.composed[2]</t>
+          <t xml:space="preserve">atk.composed.bold[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -428,7 +428,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.bold[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -443,7 +443,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.composed[3]</t>
+          <t xml:space="preserve">atk.composed.bold[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -460,7 +460,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.bold.composed[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.bold[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -475,7 +475,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.bold.composed[4]</t>
+          <t xml:space="preserve">atk.composed.bold[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -492,7 +492,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.bold[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -507,7 +507,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.composed[1]</t>
+          <t xml:space="preserve">bigmove.composed.bold[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -524,7 +524,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.bold[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -539,7 +539,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.composed[2]</t>
+          <t xml:space="preserve">bigmove.composed.bold[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -556,7 +556,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.bold.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.bold[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -571,7 +571,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.bold.composed[3]</t>
+          <t xml:space="preserve">bigmove.composed.bold[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -588,7 +588,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.bold[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -603,7 +603,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.composed[1]</t>
+          <t xml:space="preserve">climax.composed.bold[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -620,7 +620,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.bold.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.bold[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -635,7 +635,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.bold.composed[2]</t>
+          <t xml:space="preserve">climax.composed.bold[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -652,7 +652,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.bold.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.composed.bold[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.bold.composed[1]</t>
+          <t xml:space="preserve">badWinner.composed.bold[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -684,7 +684,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.bold.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.composed.bold[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -699,7 +699,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.bold.composed[1]</t>
+          <t xml:space="preserve">goodWinner.composed.bold[1]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -716,7 +716,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.bold.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.composed.bold[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -731,7 +731,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.bold.composed[1]</t>
+          <t xml:space="preserve">competition_won.composed.bold[1]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -748,7 +748,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.bold.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.composed.bold[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -763,7 +763,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.bold.composed[1]</t>
+          <t xml:space="preserve">direct.composed.bold[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -780,7 +780,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.bold.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.composed.bold[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -795,7 +795,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.bold.composed[1]</t>
+          <t xml:space="preserve">fa_signing.composed.bold[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -812,7 +812,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.composed.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.bold.hit[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -827,7 +827,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed.hit[1]</t>
+          <t xml:space="preserve">composed.bold.hit[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -844,7 +844,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.composed.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.bold.hit[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -859,7 +859,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed.hit[2]</t>
+          <t xml:space="preserve">composed.bold.hit[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -876,7 +876,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.composed.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.bold.win[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -891,7 +891,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed.win[1]</t>
+          <t xml:space="preserve">composed.bold.win[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -908,7 +908,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.composed.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.bold.win[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -923,7 +923,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed.win[2]</t>
+          <t xml:space="preserve">composed.bold.win[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -940,7 +940,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -955,7 +955,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -972,7 +972,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -987,7 +987,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1004,7 +1004,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.bold.composed[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[3]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1036,7 +1036,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1068,7 +1068,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1100,7 +1100,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.bold.composed[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[3]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1132,7 +1132,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1164,7 +1164,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1196,7 +1196,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.bold.composed[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[3]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1228,7 +1228,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1260,7 +1260,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1292,7 +1292,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.bold.composed[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[3]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1324,7 +1324,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1356,7 +1356,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1388,7 +1388,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1420,7 +1420,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1452,7 +1452,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.bold.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.composed.bold[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.bold.composed[1]</t>
+          <t xml:space="preserve">ahead.composed.bold[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1484,7 +1484,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.bold.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.composed.bold[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.bold.composed[1]</t>
+          <t xml:space="preserve">behind.composed.bold[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1516,7 +1516,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.bold.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.composed.bold[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.composed[1]</t>
+          <t xml:space="preserve">loser.composed.bold[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1548,7 +1548,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.bold.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.composed.bold[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.composed[1]</t>
+          <t xml:space="preserve">winner.composed.bold[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1580,7 +1580,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.bold.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.composed.bold[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.composed[1]</t>
+          <t xml:space="preserve">loser.composed.bold[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1612,7 +1612,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.bold.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.composed.bold[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.composed[1]</t>
+          <t xml:space="preserve">winner.composed.bold[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1644,7 +1644,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.composed.bold[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.bold[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1676,7 +1676,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.composed.bold[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.composed[1]</t>
+          <t xml:space="preserve">defender.composed.bold[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1708,7 +1708,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.composed.bold[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.bold[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1740,7 +1740,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.composed.bold[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.composed[1]</t>
+          <t xml:space="preserve">defender.composed.bold[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1772,7 +1772,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.composed.bold[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.bold.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.bold[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1804,7 +1804,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.composed.bold[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.bold.composed[1]</t>
+          <t xml:space="preserve">defender.composed.bold[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1836,7 +1836,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.composed.bold[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.bold.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.composed.bold[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1868,7 +1868,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.composed.bold[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.bold.composed[1]</t>
+          <t xml:space="preserve">fateDefender.composed.bold[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1900,7 +1900,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.composed.bold[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.bold[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1932,7 +1932,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.composed.bold[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.bold[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1964,7 +1964,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.composed.bold[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.bold.composed[1]</t>
+          <t xml:space="preserve">fateLoser.composed.bold[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1996,7 +1996,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.composed.bold[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.bold.composed[1]</t>
+          <t xml:space="preserve">fateWinner.composed.bold[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2028,7 +2028,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.composed.bold[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.bold.composed[1]</t>
+          <t xml:space="preserve">loser.composed.bold[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2060,7 +2060,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.bold.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.composed.bold[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.bold.composed[1]</t>
+          <t xml:space="preserve">winner.composed.bold[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2092,7 +2092,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.bold.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.composed.bold[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.bold.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.bold[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2124,7 +2124,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.bold.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.composed.bold[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.bold.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.bold[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2156,7 +2156,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.bold.composed[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.composed.bold[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.bold.composed[1]</t>
+          <t xml:space="preserve">awakening.composed.bold[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2956,7 +2956,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.bold[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold.composed[1]</t>
+          <t xml:space="preserve">accepted.composed.bold[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2988,7 +2988,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.bold.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.bold[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.bold.composed[2]</t>
+          <t xml:space="preserve">accepted.composed.bold[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3020,7 +3020,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.bold[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold.composed[1]</t>
+          <t xml:space="preserve">defended.composed.bold[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3052,7 +3052,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.bold.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.bold[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.bold.composed[2]</t>
+          <t xml:space="preserve">defended.composed.bold[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3084,7 +3084,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.bold[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold.composed[1]</t>
+          <t xml:space="preserve">defense_failed.composed.bold[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3116,7 +3116,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.bold.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.bold[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.bold.composed[2]</t>
+          <t xml:space="preserve">defense_failed.composed.bold[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3148,7 +3148,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.bold.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.composed.bold[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.bold.composed[1]</t>
+          <t xml:space="preserve">default.composed.bold[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3180,7 +3180,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.bold.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.composed.bold[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.bold.composed[1]</t>
+          <t xml:space="preserve">former_champ.composed.bold[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3212,7 +3212,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.bold.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.composed.bold[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.bold.composed[1]</t>
+          <t xml:space="preserve">heel.composed.bold[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3244,7 +3244,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.bold.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.composed.bold[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.bold.composed[1]</t>
+          <t xml:space="preserve">high_trust.composed.bold[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3276,7 +3276,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.composed.bold[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.bold.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.composed.bold[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3308,7 +3308,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.composed.bold[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.bold.composed[1]</t>
+          <t xml:space="preserve">accept_heel.composed.bold[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3340,7 +3340,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.composed.bold[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.bold.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.composed.bold[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3372,7 +3372,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.bold.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3404,7 +3404,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.composed.bold[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.bold.composed[1]</t>
+          <t xml:space="preserve">accept_winless.composed.bold[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3436,7 +3436,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.composed.bold[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.bold.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.composed.bold[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3468,7 +3468,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.composed.bold[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.bold.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.composed.bold[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3500,7 +3500,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.bold.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3532,7 +3532,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.bold.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.composed.bold[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.bold.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.composed.bold[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3564,7 +3564,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.bold.composed[1]</t>
+          <t xml:space="preserve">A1_champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3596,7 +3596,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.composed.bold[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.bold.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.composed.bold[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3628,7 +3628,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.composed.bold[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.bold.composed[1]</t>
+          <t xml:space="preserve">A3_heel.composed.bold[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3660,7 +3660,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.composed.bold[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.bold.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.composed.bold[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3692,7 +3692,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.composed.bold[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.bold.composed[1]</t>
+          <t xml:space="preserve">B1_young.composed.bold[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3724,7 +3724,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.composed.bold[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.bold.composed[1]</t>
+          <t xml:space="preserve">B2_prime.composed.bold[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3756,7 +3756,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.composed.bold[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.bold.composed[1]</t>
+          <t xml:space="preserve">B3_older.composed.bold[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3788,7 +3788,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.bold.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.composed.bold[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.bold.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.composed.bold[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3820,7 +3820,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3852,7 +3852,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.bold.composed[1]</t>
+          <t xml:space="preserve">raise_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3884,7 +3884,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.bold.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3916,7 +3916,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.bold.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.bold[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3948,7 +3948,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.bold.composed[1]</t>
+          <t xml:space="preserve">raise_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3980,7 +3980,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.bold[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.bold.composed[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.bold[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4012,7 +4012,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.composed[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4044,7 +4044,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.bold.composed[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.bold[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.bold.composed[2]</t>
+          <t xml:space="preserve">sudden_departure.composed.bold[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4076,7 +4076,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.bold.composed[1]</t>
+          <t xml:space="preserve">transfer_listen.composed.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4108,7 +4108,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.bold.composed[1]</t>
+          <t xml:space="preserve">transfer_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4140,7 +4140,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.bold.composed[1]</t>
+          <t xml:space="preserve">transfer_release.composed.bold[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4172,7 +4172,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.bold.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.composed.bold[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4204,7 +4204,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.bold.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.bold[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.bold.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_success.composed.bold[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4236,7 +4236,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.bold.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.bold[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.bold.composed[1]</t>
+          <t xml:space="preserve">blocked.composed.bold[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4269,7 +4269,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.bold.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.bold[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.bold.composed[1]</t>
+          <t xml:space="preserve">fail.composed.bold[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4302,7 +4302,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.bold.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.bold[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.bold.composed[1]</t>
+          <t xml:space="preserve">start.composed.bold[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4334,7 +4334,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.bold.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.bold[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.bold.composed[1]</t>
+          <t xml:space="preserve">success.composed.bold[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -5615,7 +5615,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5647,7 +5647,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5679,7 +5679,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.bold.composed[1]</t>
+          <t xml:space="preserve">cap_reached.composed.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5711,7 +5711,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.bold.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5743,7 +5743,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.bold.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5775,7 +5775,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.bold[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.bold.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.bold[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5807,7 +5807,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.bold[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.bold.composed[1]</t>
+          <t xml:space="preserve">pop_growth.composed.bold[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5839,7 +5839,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.bold.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.bold[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.bold.composed[1]</t>
+          <t xml:space="preserve">pop_star.composed.bold[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5871,7 +5871,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5903,7 +5903,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5935,7 +5935,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5967,7 +5967,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.bold.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.bold.composed[1]</t>
+          <t xml:space="preserve">defeat.composed.bold[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5999,7 +5999,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.bold.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.bold.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.bold[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6031,7 +6031,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.bold.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.bold[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.bold.composed[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.bold[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6063,7 +6063,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.bold.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.bold[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.bold.composed[1]</t>
+          <t xml:space="preserve">penalty_end.composed.bold[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6095,7 +6095,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.bold.composed[1]</t>
+          <t xml:space="preserve">bestMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6127,7 +6127,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.composed[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6159,7 +6159,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.bold[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.bold.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.bold[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6191,7 +6191,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.bold[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.bold.composed[1]</t>
+          <t xml:space="preserve">mediaAward.composed.bold[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6223,7 +6223,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.bold.composed[1]</t>
+          <t xml:space="preserve">mvp.composed.bold[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6255,7 +6255,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.bold.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.bold[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.bold.composed[1]</t>
+          <t xml:space="preserve">rookie.composed.bold[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6287,7 +6287,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6319,7 +6319,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6351,7 +6351,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.bold.composed[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[3]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6383,7 +6383,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6415,7 +6415,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6447,7 +6447,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.bold.composed[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[3]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6479,7 +6479,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.bold.composed[1]</t>
+          <t xml:space="preserve">N1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6511,7 +6511,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.bold[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.bold.composed[1]</t>
+          <t xml:space="preserve">N2.composed.bold[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6543,7 +6543,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.bold.composed[1]</t>
+          <t xml:space="preserve">N3.composed.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6575,7 +6575,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.bold.composed[1]</t>
+          <t xml:space="preserve">N4.composed.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6607,7 +6607,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.bold.composed[1]</t>
+          <t xml:space="preserve">N5_low.composed.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6639,7 +6639,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.bold.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.bold.composed[1]</t>
+          <t xml:space="preserve">N5_warning.composed.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6671,7 +6671,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.bold.composed[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6703,7 +6703,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.bold.composed[1]</t>
+          <t xml:space="preserve">G1.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6735,7 +6735,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.bold.composed[1]</t>
+          <t xml:space="preserve">G2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6767,7 +6767,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.bold.composed[1]</t>
+          <t xml:space="preserve">G3.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6799,7 +6799,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.bold.composed[1]</t>
+          <t xml:space="preserve">G4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6831,7 +6831,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.bold.composed[1]</t>
+          <t xml:space="preserve">R2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6863,7 +6863,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.bold.composed[1]</t>
+          <t xml:space="preserve">R3.modal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6895,7 +6895,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.bold.composed[1]</t>
+          <t xml:space="preserve">R4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6927,7 +6927,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.bold.composed[1]</t>
+          <t xml:space="preserve">R5.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6959,7 +6959,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.bold.composed[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.bold.composed[1]</t>
+          <t xml:space="preserve">warVictory.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6991,7 +6991,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.bold.composed[1]</t>
+          <t xml:space="preserve">bonus.composed.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7023,7 +7023,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.bold.composed[1]</t>
+          <t xml:space="preserve">camp.composed.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7055,7 +7055,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.bold.composed[1]</t>
+          <t xml:space="preserve">encourage_high_trust.composed.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7087,7 +7087,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.bold.composed[1]</t>
+          <t xml:space="preserve">encourage.composed.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7119,7 +7119,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.bold.composed[1]</t>
+          <t xml:space="preserve">faction_decree.composed.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7151,7 +7151,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.bold.composed[1]</t>
+          <t xml:space="preserve">media.composed.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7183,7 +7183,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.bold.composed[1]</t>
+          <t xml:space="preserve">party.composed.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7215,7 +7215,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.bold.composed[1]</t>
+          <t xml:space="preserve">refresh_leave.composed.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7247,7 +7247,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.bold.composed[1]</t>
+          <t xml:space="preserve">special_treatment.composed.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7279,7 +7279,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.bold.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.bold.composed[1]</t>
+          <t xml:space="preserve">trainer.composed.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7311,7 +7311,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.bold.composed[1]</t>
+          <t xml:space="preserve">E1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7343,7 +7343,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.bold.composed[1]</t>
+          <t xml:space="preserve">E6.composed.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7375,7 +7375,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.bold.composed[1]</t>
+          <t xml:space="preserve">S_boycott.composed.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7407,7 +7407,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.bold.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.bold.composed[2]</t>
+          <t xml:space="preserve">S_boycott.composed.bold[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7439,7 +7439,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.bold.composed[1]</t>
+          <t xml:space="preserve">S_grumble.composed.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7471,7 +7471,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.bold.composed[1]</t>
+          <t xml:space="preserve">S_sns.composed.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7503,7 +7503,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.bold.composed[1]</t>
+          <t xml:space="preserve">S1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7535,7 +7535,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.bold.composed[1]</t>
+          <t xml:space="preserve">S2.composed.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7567,7 +7567,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.bold.composed[1]</t>
+          <t xml:space="preserve">S3.composed.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7599,7 +7599,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.bold.composed[1]</t>
+          <t xml:space="preserve">S4_direct.composed.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7631,7 +7631,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.bold.composed[1]</t>
+          <t xml:space="preserve">S4_silent.composed.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7663,7 +7663,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.bold.composed[1]</t>
+          <t xml:space="preserve">S5.composed.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7695,7 +7695,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.bold.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.bold.composed[1]</t>
+          <t xml:space="preserve">S6.composed.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7727,7 +7727,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.bold.composed[1]</t>
+          <t xml:space="preserve">B1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7759,7 +7759,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.bold.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7791,7 +7791,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.bold.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7823,7 +7823,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.bold.composed[1]</t>
+          <t xml:space="preserve">B4_brand.composed.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7855,7 +7855,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.bold.composed[1]</t>
+          <t xml:space="preserve">B4_cm.composed.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7887,7 +7887,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.bold.composed[1]</t>
+          <t xml:space="preserve">B4_fan.composed.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7919,7 +7919,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.bold.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[2]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.bold.composed[2]</t>
+          <t xml:space="preserve">B4_fan.composed.bold[2]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7951,7 +7951,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.bold.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7983,7 +7983,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.bold.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.bold.composed[2]</t>
+          <t xml:space="preserve">B4_fashion.composed.bold[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8015,7 +8015,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.bold.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.bold[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8047,7 +8047,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.bold.composed[1]</t>
+          <t xml:space="preserve">B4_variety.composed.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8079,7 +8079,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.bold.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.bold.composed[1]</t>
+          <t xml:space="preserve">B4.composed.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8111,7 +8111,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8143,7 +8143,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8175,7 +8175,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8207,7 +8207,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8239,7 +8239,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8271,7 +8271,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8303,7 +8303,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8335,7 +8335,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.bold.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8367,7 +8367,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.bold.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8399,7 +8399,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold.composed[1]</t>
+          <t xml:space="preserve">draftInterest.composed.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8431,7 +8431,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.composed[1]</t>
+          <t xml:space="preserve">draftJoin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8463,7 +8463,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold.composed[2]</t>
+          <t xml:space="preserve">draftJoin.composed.bold[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8495,7 +8495,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.bold.composed[1]</t>
+          <t xml:space="preserve">faGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8527,7 +8527,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.bold[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold.composed[1]</t>
+          <t xml:space="preserve">faSigning.composed.bold[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8559,7 +8559,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold.composed[1]</t>
+          <t xml:space="preserve">faWelcome.composed.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.composed[1]</t>
+          <t xml:space="preserve">injury.composed.bold[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8623,7 +8623,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold.composed[2]</t>
+          <t xml:space="preserve">injury.composed.bold[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8655,7 +8655,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.composed[1]</t>
+          <t xml:space="preserve">release.composed.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8687,7 +8687,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold.composed[2]</t>
+          <t xml:space="preserve">release.composed.bold[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8719,7 +8719,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold.composed[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8751,7 +8751,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.bold.composed[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8783,7 +8783,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold.composed[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8815,7 +8815,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold.composed[1]</t>
+          <t xml:space="preserve">titleDefense.composed.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8847,7 +8847,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold.composed[1]</t>
+          <t xml:space="preserve">titleLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8879,7 +8879,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8911,7 +8911,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8943,7 +8943,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8975,7 +8975,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9007,7 +9007,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9039,7 +9039,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9071,7 +9071,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9103,7 +9103,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9487,7 +9487,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9519,7 +9519,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.composed[1]</t>
+          <t xml:space="preserve">preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9551,7 +9551,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.bold.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.composed[2]</t>
+          <t xml:space="preserve">preFinal.composed.bold[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9583,7 +9583,7 @@
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.composed[1]</t>
+          <t xml:space="preserve">preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9615,7 +9615,7 @@
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.bold.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.composed[2]</t>
+          <t xml:space="preserve">preMatch.composed.bold[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9647,7 +9647,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.composed[1]</t>
+          <t xml:space="preserve">survivor.composed.bold[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9679,7 +9679,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.bold.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.bold.composed[2]</t>
+          <t xml:space="preserve">survivor.composed.bold[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9711,7 +9711,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.composed[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9743,7 +9743,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.bold.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9758,7 +9758,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.composed[2]</t>
+          <t xml:space="preserve">champion.composed.bold[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9775,7 +9775,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.composed[1]</t>
+          <t xml:space="preserve">defiant.composed.bold[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9807,7 +9807,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.bold.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.bold.composed[2]</t>
+          <t xml:space="preserve">defiant.composed.bold[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9839,7 +9839,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.composed[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.composed[1]</t>
+          <t xml:space="preserve">gauntlet.composed.bold[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9871,7 +9871,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.bold.composed[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.bold.composed[2]</t>
+          <t xml:space="preserve">gauntlet.composed.bold[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9903,7 +9903,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.bold.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.bold.composed[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9935,7 +9935,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.bold.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.bold.composed[1]</t>
+          <t xml:space="preserve">postLose.composed.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9967,7 +9967,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.bold.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.bold.composed[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9999,7 +9999,7 @@
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.bold.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.bold.composed[1]</t>
+          <t xml:space="preserve">postWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10031,7 +10031,7 @@
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.bold.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.bold.composed[1]</t>
+          <t xml:space="preserve">preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10063,7 +10063,7 @@
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.bold.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.bold.composed[1]</t>
+          <t xml:space="preserve">preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10095,7 +10095,7 @@
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.bold.composed[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.bold[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.bold.composed[1]</t>
+          <t xml:space="preserve">summon.composed.bold[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10127,7 +10127,7 @@
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10159,7 +10159,7 @@
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10191,7 +10191,7 @@
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.composed[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10223,7 +10223,7 @@
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.bold.composed[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[2]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10255,7 +10255,7 @@
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.bold.composed[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.bold[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10287,7 +10287,7 @@
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.bold.composed[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.bold[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.bold.composed[1]</t>
+          <t xml:space="preserve">result_lose.composed.bold[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10319,7 +10319,7 @@
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.bold.composed[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.bold.composed[1]</t>
+          <t xml:space="preserve">result_win.composed.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10351,7 +10351,7 @@
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10383,7 +10383,7 @@
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.bold.composed[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[2]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10415,7 +10415,7 @@
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.bold.composed[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.bold[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.bold.composed[1]</t>
+          <t xml:space="preserve">fighter.composed.bold[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10447,7 +10447,7 @@
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10479,7 +10479,7 @@
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.bold.composed[1]</t>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">

--- a/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(鷹揚×強気)に該当するキャラクター: 3名</t>
+          <t xml:space="preserve">このタイプ(鷹揚×強気)に該当するキャラクター: 4名</t>
         </is>
       </c>
     </row>
@@ -295,6 +295,28 @@
       <c r="D6" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">ヒール適性</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">山本理香</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Striker</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Neutral</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">頑丈さ</t>
         </is>
       </c>
     </row>
@@ -306,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -485,7 +507,7 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたしの全部、受け止めて</t>
+          <t xml:space="preserve">…私の全部、受け止めて</t>
         </is>
       </c>
     </row>
@@ -549,7 +571,7 @@
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見ていて…わたしの全力</t>
+          <t xml:space="preserve">…見ていて…私の全力</t>
         </is>
       </c>
     </row>
@@ -613,7 +635,7 @@
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…ここから、あたしの時間だね）</t>
+          <t xml:space="preserve">（…ここから、私の時間だね）</t>
         </is>
       </c>
     </row>
@@ -741,7 +763,7 @@
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたしを巡って争奪戦か。…期待に応えるよ</t>
+          <t xml:space="preserve">…私を巡って争奪戦か。…期待に応えるよ</t>
         </is>
       </c>
     </row>
@@ -933,7 +955,7 @@
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">要らないって言われた側だけど…ま、こんなもんかな。見えてた?</t>
+          <t xml:space="preserve">要らないって言われた側だけど…ま、こんなもんかな。見えてた？</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1371,7 @@
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたしのミスだ、{partner}。でも、次はこうはいかないよ。</t>
+          <t xml:space="preserve">…私のミスだ、{partner}。でも、次はこうはいかないよ。</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2203,7 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が静かに{nameA}の前に立った。「…もういいだろう。受けて立つよ」</t>
+          <t xml:space="preserve">{nameB}が静かに{nameA}の前に立った。「…もう十分だ。受けて立つよ」</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2683,7 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだんだ。……せいぜい、悔やまないように。</t>
+          <t xml:space="preserve">私を選んだんだ。……せいぜい、悔やまないように。</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2747,7 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう終わり方は、わたしの趣味じゃない。</t>
+          <t xml:space="preserve">こういう終わり方は、私の趣味じゃない。</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2907,7 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ほら、言った通りだろ。</t>
+          <t xml:space="preserve">……ほら、言った通りだよ。</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2939,7 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを選んだのが、間違いだったね。</t>
+          <t xml:space="preserve">私を選んだのが、間違いだったね。</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3739,7 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嘘だろ。…まだ、始まったばかりなのに</t>
+          <t xml:space="preserve">…嘘だ。…まだ、始まったばかりなのに</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4414,7 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、私たちのメンバーに、もう少し目を配っていただけませんか。</t>
+          <t xml:space="preserve">社長。うちの子たちにも、もう少し目を向けてほしいんだ。</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4574,7 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。</t>
+          <t xml:space="preserve">…わかった。言うだけは言ったんだ、それでいいよ。</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4606,7 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく受け取ります。</t>
+          <t xml:space="preserve">…なるほど、そういう形なんだ。ありがたく受け取っておくよ。</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4638,7 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがたく頂戴します。期待は超えてみせます。</t>
+          <t xml:space="preserve">ありがたく頂いておくよ。期待はきっちり超えてみせるから、見てて。</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4798,7 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういうご配慮ですか。ありがたく頂戴します。</t>
+          <t xml:space="preserve">…なるほど、そこまで気を回してくれたんだ。素直に甘えておこうかな。</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4862,7 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。出過ぎたことを申しました。</t>
+          <t xml:space="preserve">…そう。なら引くよ。言いたいことは伝わったはずだ。</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4894,7 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく受け取ります。</t>
+          <t xml:space="preserve">…ふぅん、そう来たんだ。せっかくだし、遠慮なくもらっておこうかな。</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5182,7 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。ありがたく頂戴します。</t>
+          <t xml:space="preserve">…へえ、そういうことか。その気遣い、ありがたく乗らせてもらうよ。</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5470,7 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがたく頂戴します。</t>
+          <t xml:space="preserve">…その心遣い、素直に嬉しいよ。</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5566,7 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、下の子のケアですか。ありがたく頂戴します。</t>
+          <t xml:space="preserve">…なるほど、下の子たちのケアってわけだ。その心遣いには感謝するよ。</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5630,7 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等。受けて立とう</t>
+          <t xml:space="preserve">いいね、受けて立つ</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6117,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6110,7 +6132,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6120,14 +6142,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい試合だった。出し惜しみなんてできなかったよ</t>
+          <t xml:space="preserve">この対抗戦は私たちが制した。次も同じだ。</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6142,7 +6164,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[1]</t>
+          <t xml:space="preserve">bestMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6152,14 +6174,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが頂点。渡す気はないよ</t>
+          <t xml:space="preserve">…いい試合だった。出し惜しみなんてできなかったよ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6174,7 +6196,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.bold[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6184,14 +6206,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全部やりきった。悔いはないよ</t>
+          <t xml:space="preserve">…ここが頂点。渡す気はないよ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.bold[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6206,7 +6228,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.composed.bold[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.bold[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6216,14 +6238,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…リングの外でも、やるべきことをやっただけだよ</t>
+          <t xml:space="preserve">…全部やりきった。悔いはないよ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6238,7 +6260,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.bold[1]</t>
+          <t xml:space="preserve">mediaAward.composed.bold[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6248,14 +6270,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、結果は出したからね。…でもまだ先がある</t>
+          <t xml:space="preserve">…リングの外でも、やるべきことをやっただけだよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.bold[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6270,7 +6292,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.bold[1]</t>
+          <t xml:space="preserve">mvp.composed.bold[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6280,14 +6302,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…通過点だね。次を見てなよ</t>
+          <t xml:space="preserve">…まあ、結果は出したからね。…でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6297,12 +6319,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">rookie.composed.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6312,14 +6334,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム。燃える。それだけだ</t>
+          <t xml:space="preserve">…通過点だね。次を見てなよ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6329,12 +6351,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">springTagChampion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6344,14 +6366,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことは分かってる。全力でぶつかる</t>
+          <t xml:space="preserve">春の頂点は私たちのもの。次も譲る気はない。</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6366,7 +6388,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[3]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6376,14 +6398,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この闘志、ドームで解き放つ</t>
+          <t xml:space="preserve">ドーム、か。…燃えてきたな</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6393,12 +6415,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6408,14 +6430,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。…達成感しかない</t>
+          <t xml:space="preserve">…やるべきことは分かってる。全力でぶつかる</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6425,12 +6447,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6440,14 +6462,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でやった。それが報われた</t>
+          <t xml:space="preserve">この闘志、ドームで全部見せてあげるよ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6462,7 +6484,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[3]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6472,14 +6494,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと上を目指す</t>
+          <t xml:space="preserve">満員。…達成感しかない</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6489,29 +6511,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ先がある。焦らず行くよ</t>
+          <t xml:space="preserve">全力でやった。それが報われた</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6521,29 +6543,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないチームだよ。居心地がいい</t>
+          <t xml:space="preserve">次はもっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6558,7 +6580,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.bold[1]</t>
+          <t xml:space="preserve">N1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6568,14 +6590,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この程度なら大丈夫。慌てないで</t>
+          <t xml:space="preserve">…まだ先がある。焦らず行くよ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6590,7 +6612,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.bold[1]</t>
+          <t xml:space="preserve">N2.composed.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6600,14 +6622,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないね。この期待に応えるだけだよ</t>
+          <t xml:space="preserve">…悪くないチームだよ。居心地がいい</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.bold[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6622,7 +6644,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.bold[1]</t>
+          <t xml:space="preserve">N3.composed.bold[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6632,14 +6654,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいる意味、少し考え直してもいいかな</t>
+          <t xml:space="preserve">…この程度なら大丈夫。慌てないで</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.bold[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6654,7 +6676,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.bold[1]</t>
+          <t xml:space="preserve">N4.composed.bold[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6664,14 +6686,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、少し立ち止まってるだけだよ。…たぶん</t>
+          <t xml:space="preserve">…悪くないね。この期待に応えるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6681,12 +6703,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.composed.bold[1]</t>
+          <t xml:space="preserve">N5_low.composed.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6696,14 +6718,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ先がある。…ここでなら</t>
+          <t xml:space="preserve">…ここにいる意味、少し考え直してもいいかな</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.bold[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6713,12 +6735,12 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.composed.bold[1]</t>
+          <t xml:space="preserve">N5_warning.composed.bold[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6728,14 +6750,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。…まあ、いいけど</t>
+          <t xml:space="preserve">…ま、少し立ち止まってるだけだよ。…たぶん</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6750,7 +6772,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.composed.bold[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6760,14 +6782,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるね。…でも、まだ負けるつもりはない</t>
+          <t xml:space="preserve">…まだ先がある。…ここでなら</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6782,7 +6804,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.composed.bold[1]</t>
+          <t xml:space="preserve">G1.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6792,14 +6814,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。…まだ順番が来ないか</t>
+          <t xml:space="preserve">…ふぅん。…まあ、いいけど</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6814,7 +6836,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.composed.bold[1]</t>
+          <t xml:space="preserve">G2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6824,14 +6846,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…使ってくれないと、困るんだけど</t>
+          <t xml:space="preserve">…やるね。…でも、まだ負けるつもりはない</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6846,7 +6868,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.composed.bold[1]</t>
+          <t xml:space="preserve">G3.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6856,14 +6878,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、いいんだけどね。一人でも</t>
+          <t xml:space="preserve">…ふぅん。…まだ順番が来ないか</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6878,7 +6900,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.composed.bold[1]</t>
+          <t xml:space="preserve">G4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6888,14 +6910,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くんだ。…まあ、{name2}が決めたことだからね</t>
+          <t xml:space="preserve">…使ってくれないと、困るんだけど</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6910,7 +6932,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.composed.bold[1]</t>
+          <t xml:space="preserve">R2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6920,14 +6942,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…でも、まだだね</t>
+          <t xml:space="preserve">…まあ、いいんだけどね。一人でも</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6942,7 +6964,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.composed.bold[1]</t>
+          <t xml:space="preserve">R3.modal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6952,14 +6974,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は返す。…覚えておいて</t>
+          <t xml:space="preserve">…行くんだ。…まあ、{name2}が決めたことだからね</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6974,7 +6996,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.composed.bold[1]</t>
+          <t xml:space="preserve">R4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6984,14 +7006,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…うちの看板、守れたかな</t>
+          <t xml:space="preserve">…勝った。…でも、まだだね</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7001,29 +7023,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.composed.bold[1]</t>
+          <t xml:space="preserve">R5.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。結果で返すよ</t>
+          <t xml:space="preserve">…次は返す。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7033,29 +7055,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.composed.bold[1]</t>
+          <t xml:space="preserve">warVictory.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。しっかり追い込むよ</t>
+          <t xml:space="preserve">…勝った。…うちの看板、守れたかな</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7070,7 +7092,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.composed.bold[1]</t>
+          <t xml:space="preserve">bonus.composed.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7080,14 +7102,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…信じてくれるなら、応えないとね</t>
+          <t xml:space="preserve">…ありがとう。結果で返すよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7102,7 +7124,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.composed.bold[1]</t>
+          <t xml:space="preserve">camp.composed.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7112,14 +7134,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ終わってないよ。やるだけやる</t>
+          <t xml:space="preserve">…いい機会だね。しっかり追い込むよ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7134,7 +7156,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.bold[1]</t>
+          <t xml:space="preserve">encourage_high_trust.composed.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7144,14 +7166,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……納得はしていない。それだけは言っておくよ</t>
+          <t xml:space="preserve">…信じてくれるなら、応えないとね</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7166,7 +7188,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.composed.bold[1]</t>
+          <t xml:space="preserve">encourage.composed.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7176,14 +7198,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。任せて</t>
+          <t xml:space="preserve">…まだ終わってないよ。やるだけやる</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7198,7 +7220,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.composed.bold[1]</t>
+          <t xml:space="preserve">faction_decree.composed.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7208,14 +7230,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい雰囲気だね。こういうのも大事だよ</t>
+          <t xml:space="preserve">……納得はしていない。それだけは言っておくよ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7230,7 +7252,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.composed.bold[1]</t>
+          <t xml:space="preserve">media.composed.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7240,14 +7262,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…充電してくるよ。戻ったらまた行こう</t>
+          <t xml:space="preserve">…いい機会だね。任せて</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7262,7 +7284,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.composed.bold[1]</t>
+          <t xml:space="preserve">party.composed.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7272,14 +7294,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…早く戻るよ。ありがとう</t>
+          <t xml:space="preserve">…いい雰囲気だね。こういうのも大事だよ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7294,7 +7316,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.composed.bold[1]</t>
+          <t xml:space="preserve">refresh_leave.composed.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7304,14 +7326,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。無駄にはしないよ</t>
+          <t xml:space="preserve">…充電してくるよ。戻ったらまた行こう</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7321,12 +7343,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.bold[1]</t>
+          <t xml:space="preserve">special_treatment.composed.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7336,14 +7358,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないね。いつも通りやるよ</t>
+          <t xml:space="preserve">…早く戻るよ。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7353,12 +7375,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.bold[1]</t>
+          <t xml:space="preserve">trainer.composed.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7368,14 +7390,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない条件なんだよね。…少し考えてもいいかな</t>
+          <t xml:space="preserve">…いい機会だね。無駄にはしないよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7390,7 +7412,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.bold[1]</t>
+          <t xml:space="preserve">E1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7400,14 +7422,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出してもらえないのに、練習する意味あるのかな</t>
+          <t xml:space="preserve">…悪くないね。いつも通りやるよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7422,7 +7444,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.bold[2]</t>
+          <t xml:space="preserve">E6.composed.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7432,14 +7454,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…リングに上がれないなら、同じことだよ</t>
+          <t xml:space="preserve">…悪くない条件なんだよね。…少し考えてもいいかな</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7454,7 +7476,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.bold[1]</t>
+          <t xml:space="preserve">S_boycott.composed.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7464,14 +7486,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「…この扱いは、さすがに通らないよ」と静かに言い切り、場が凍りついた）</t>
+          <t xml:space="preserve">…出してもらえないのに、練習する意味あるのかな</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7486,7 +7508,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.bold[1]</t>
+          <t xml:space="preserve">S_boycott.composed.bold[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7496,14 +7518,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「…このまま終わるつもりはないよ」と静かな宣言を投稿）</t>
+          <t xml:space="preserve">…リングに上がれないなら、同じことだよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7518,7 +7540,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.bold[1]</t>
+          <t xml:space="preserve">S_grumble.composed.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7528,14 +7550,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルト、狙わせてもらうよ。組んでくれる？</t>
+          <t xml:space="preserve">（「…この扱いは、さすがに通らないよ」と静かに言い切り、場が凍りついた）</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7550,7 +7572,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.bold[1]</t>
+          <t xml:space="preserve">S_sns.composed.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7560,14 +7582,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決着をつけたいんだ。組んでくれないかな</t>
+          <t xml:space="preserve">（SNSに「…このまま終わるつもりはないよ」と静かな宣言を投稿）</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7582,7 +7604,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.bold[1]</t>
+          <t xml:space="preserve">S1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7592,14 +7614,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が限界みたいだ。少し休むよ</t>
+          <t xml:space="preserve">…ベルト、狙わせてもらうよ。組んでくれる？</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7614,7 +7636,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.bold[1]</t>
+          <t xml:space="preserve">S2.composed.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7624,14 +7646,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままだと先がないよ。考え直してくれないかな</t>
+          <t xml:space="preserve">…決着をつけたいんだ。組んでくれないかな</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7646,7 +7668,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.bold[1]</t>
+          <t xml:space="preserve">S3.composed.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7656,14 +7678,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（拳を握り、それから静かに息を吐いた）</t>
+          <t xml:space="preserve">…体が限界みたいだ。少し休むよ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7678,7 +7700,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.bold[1]</t>
+          <t xml:space="preserve">S4_direct.composed.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7688,14 +7710,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し上に行きたい。特訓させてくれないかな</t>
+          <t xml:space="preserve">…このままだと先がないよ。考え直してくれないかな</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.bold[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7710,7 +7732,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.bold[1]</t>
+          <t xml:space="preserve">S4_silent.composed.bold[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7720,14 +7742,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩に伝えておきたいことがあるんだ。任せてくれないかな</t>
+          <t xml:space="preserve">…………（拳を握り、それから静かに息を吐いた）</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7737,12 +7759,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.bold[1]</t>
+          <t xml:space="preserve">S5.composed.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7752,14 +7774,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、こういうこともあるよ。少し待ってて</t>
+          <t xml:space="preserve">…もう少し上に行きたい。特訓させてくれないかな</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7769,12 +7791,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.bold[1]</t>
+          <t xml:space="preserve">S6.composed.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7784,14 +7806,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪いけど、あの人とはちょっと厳しいかな</t>
+          <t xml:space="preserve">…後輩に伝えておきたいことがあるんだ。任せてくれないかな</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7806,7 +7828,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.bold[1]</t>
+          <t xml:space="preserve">B1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7816,14 +7838,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私は私のやり方を変えるつもりはないよ。それだけ</t>
+          <t xml:space="preserve">…まあ、こういうこともあるよ。少し待ってて</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7838,7 +7860,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.bold[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7848,14 +7870,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない組み合わせだね。いいものにしよう</t>
+          <t xml:space="preserve">…悪いけど、あの人とはちょっと厳しいかな</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7870,7 +7892,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.bold[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7880,14 +7902,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全国か。いい機会だね、自分のペースでやるよ</t>
+          <t xml:space="preserve">…私は私のやり方を変えるつもりはないよ。それだけ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7902,7 +7924,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.bold[1]</t>
+          <t xml:space="preserve">B4_brand.composed.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7912,14 +7934,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の思い出を持って帰ってもらおうか</t>
+          <t xml:space="preserve">…悪くない組み合わせだね。いいものにしよう</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7934,7 +7956,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.bold[2]</t>
+          <t xml:space="preserve">B4_cm.composed.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7944,14 +7966,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全員笑顔で帰す。…それが私の仕事だからね</t>
+          <t xml:space="preserve">…全国か。いい機会だね、自分のペースでやるよ</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7966,7 +7988,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.bold[1]</t>
+          <t xml:space="preserve">B4_fan.composed.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7976,14 +7998,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ランウェイも私の舞台だよ。…全部持っていく</t>
+          <t xml:space="preserve">…最高の思い出を持って帰ってもらおうか</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[2]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7998,7 +8020,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.bold[2]</t>
+          <t xml:space="preserve">B4_fan.composed.bold[2]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8008,14 +8030,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…プロレスもファッションも。…どっちも私のものだね</t>
+          <t xml:space="preserve">…全員笑顔で帰す。…それが私の仕事だからね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8030,7 +8052,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8040,14 +8062,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…撮られるのは嫌いじゃないよ。いい写真にしよう</t>
+          <t xml:space="preserve">…ランウェイも私の舞台だよ。…全部持っていく</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[2]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8062,7 +8084,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.bold[2]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8072,14 +8094,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、自分のペースで話せばいいんでしょ。大丈夫</t>
+          <t xml:space="preserve">…プロレスもファッションも。…どっちも私のものだね</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8094,7 +8116,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.bold[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8104,14 +8126,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。自分らしくやらせてもらうよ</t>
+          <t xml:space="preserve">…撮られるのは嫌いじゃないよ。いい写真にしよう</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8121,29 +8143,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">B4_variety.composed.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
+          <t xml:space="preserve">…まあ、自分のペースで話せばいいんでしょ。大丈夫</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8153,29 +8175,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">B4.composed.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">…いい機会だね。自分らしくやらせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8185,12 +8207,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8200,14 +8222,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待には応える。見ててくれ</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8217,7 +8239,7 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
@@ -8239,7 +8261,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8249,12 +8271,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8264,14 +8286,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点まで。…見ていて</t>
+          <t xml:space="preserve">…期待には応える。見ていて</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8281,7 +8303,7 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
@@ -8296,14 +8318,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8313,12 +8335,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8328,14 +8350,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…問題ない。少し休めば治る</t>
+          <t xml:space="preserve">…頂点まで。…見ていて</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8345,12 +8367,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8360,14 +8382,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…片付いた相手だよ。…なのに、まだ目で追ってる</t>
+          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8377,12 +8399,12 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8392,14 +8414,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった話らしいね。…じゃあ、この重さは何なんだろう</t>
+          <t xml:space="preserve">…問題ない。少し休めば治る</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8414,7 +8436,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8424,14 +8446,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
+          <t xml:space="preserve">…片付いた相手だよ。…なのに、まだ目で追ってる</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8446,7 +8468,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8456,14 +8478,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">…終わった話らしいね。…じゃあ、この重さは何なんだろう</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.bold[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8478,7 +8500,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.bold[2]</t>
+          <t xml:space="preserve">draftInterest.composed.bold[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8488,14 +8510,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待には応える。見ててくれ</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8510,7 +8532,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">draftJoin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8520,14 +8542,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[2]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8542,7 +8564,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.bold[1]</t>
+          <t xml:space="preserve">draftJoin.composed.bold[2]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8552,14 +8574,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">…期待には応える。見ていて</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8574,7 +8596,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.bold[1]</t>
+          <t xml:space="preserve">faGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8584,14 +8606,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点まで。…見ていて</t>
+          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.bold[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8606,7 +8628,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.bold[1]</t>
+          <t xml:space="preserve">faSigning.composed.bold[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8616,14 +8638,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8638,7 +8660,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.bold[2]</t>
+          <t xml:space="preserve">faWelcome.composed.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8648,14 +8670,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…問題ない。少し休めば治る</t>
+          <t xml:space="preserve">…頂点まで。…見ていて</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8670,7 +8692,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.bold[1]</t>
+          <t xml:space="preserve">injury.composed.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8680,14 +8702,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
+          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8702,7 +8724,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.bold[2]</t>
+          <t xml:space="preserve">injury.composed.bold[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8712,14 +8734,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
+          <t xml:space="preserve">…問題ない。少し休めば治る</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8734,7 +8756,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">release.composed.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8744,14 +8766,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
+          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8766,7 +8788,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">release.composed.bold[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8776,14 +8798,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…目は確かみたいだね。まぁ…頑張るよ</t>
+          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8798,7 +8820,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.bold[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8808,14 +8830,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
+          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8830,7 +8852,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8840,14 +8862,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
+          <t xml:space="preserve">…目は確かみたいだね。まぁ…頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8862,7 +8884,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8872,14 +8894,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…取り返す。…覚えておいて</t>
+          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.bold[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8894,7 +8916,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.bold[1]</t>
+          <t xml:space="preserve">titleDefense.composed.bold[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8904,14 +8926,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
+          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8921,12 +8943,12 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">titleLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8936,14 +8958,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
+          <t xml:space="preserve">…取り返す。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8953,12 +8975,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">titleWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8968,14 +8990,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
+          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8985,7 +9007,7 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
@@ -9000,14 +9022,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
+          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9017,12 +9039,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9032,14 +9054,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
+          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9049,7 +9071,7 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
@@ -9064,14 +9086,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
+          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9081,7 +9103,7 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
@@ -9096,14 +9118,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…取り返す。…覚えておいて</t>
+          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9113,7 +9135,7 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
@@ -9128,14 +9150,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
+          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9145,29 +9167,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無理なものは無理。…それだけ</t>
+          <t xml:space="preserve">…取り返す。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9177,29 +9199,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…壁作ってない？ …まあ、いいけど</t>
+          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9214,7 +9236,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9224,14 +9246,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なかなかやるね。認めてあげてもいいかな</t>
+          <t xml:space="preserve">…無理なものは無理。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9246,7 +9268,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9256,14 +9278,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の相棒だね。…二人なら怖いものはない</t>
+          <t xml:space="preserve">…壁作ってない？ …まあ、いいけど</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9278,7 +9300,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9288,14 +9310,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった。…次に行くよ</t>
+          <t xml:space="preserve">…なかなかやるね。認めてあげてもいいかな</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9310,7 +9332,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9320,14 +9342,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…面白い相手だね。…超えてみせるよ</t>
+          <t xml:space="preserve">…最高の相棒だね。…二人なら怖いものはない</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9342,7 +9364,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9352,14 +9374,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の敵だね。…超える。それだけ</t>
+          <t xml:space="preserve">…終わった。…次に行くよ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9374,7 +9396,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.composed[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9384,14 +9406,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…生涯の勝負だ。…望むところ</t>
+          <t xml:space="preserve">…面白い相手だね。…超えてみせるよ</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9406,7 +9428,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.composed[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9416,14 +9438,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが最高の場所だ。…もっと強くしてみせる</t>
+          <t xml:space="preserve">…最高の敵だね。…超える。それだけ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9438,7 +9460,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.composed[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9448,14 +9470,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう付き合いきれないかな。…覚えておいて</t>
+          <t xml:space="preserve">…生涯の勝負だ。…望むところ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.composed[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9470,7 +9492,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.composed[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.composed[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9480,14 +9502,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この扱いは、ちょっとどうかと思うけど</t>
+          <t xml:space="preserve">…ここが最高の場所だ。…もっと強くしてみせる</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.composed[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9497,12 +9519,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.composed[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9512,14 +9534,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻ったね。…あの感覚は覚えた</t>
+          <t xml:space="preserve">…もう付き合いきれないかな。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.composed[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9529,29 +9551,29 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.composed[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は重い。でも、最後の舞台を降りる理由にはならないよ</t>
+          <t xml:space="preserve">…この扱いは、ちょっとどうかと思うけど</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9561,29 +9583,29 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.bold[2]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た者だけが立てる場所だ。…受けて立つ</t>
+          <t xml:space="preserve">…戻ったね。…あの感覚は覚えた</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9598,7 +9620,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9608,14 +9630,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰でも、受けて立つよ。慌てる場面じゃない</t>
+          <t xml:space="preserve">…身体は重い。でも、最後の舞台を降りる理由にはならないよ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9630,7 +9652,7 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.bold[2]</t>
+          <t xml:space="preserve">preFinal.composed.bold[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9640,14 +9662,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人でも並びなよ。…上等。並んだだけ、倒すから</t>
+          <t xml:space="preserve">ここまで来た者だけが立てる場所だ。…受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9662,7 +9684,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.bold[1]</t>
+          <t xml:space="preserve">preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9672,14 +9694,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人片づけたよ。息は上がってるけど、退く場面じゃない。次、来なよ</t>
+          <t xml:space="preserve">相手が誰でも、受けて立つよ。慌てる場面じゃない</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9694,7 +9716,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.bold[2]</t>
+          <t xml:space="preserve">preMatch.composed.bold[2]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9704,14 +9726,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ拳は握れる。…このリングは渡さないよ。次は誰だ</t>
+          <t xml:space="preserve">何人でも並びなよ。…上等。並んだだけ、倒すから</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9721,12 +9743,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[1]</t>
+          <t xml:space="preserve">survivor.composed.bold[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9736,14 +9758,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人が揃えば……どの団体にも、負ける道理はなかった</t>
+          <t xml:space="preserve">…一人片づけたよ。息は上がってるけど、退く場面じゃない。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9753,12 +9775,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[2]</t>
+          <t xml:space="preserve">survivor.composed.bold[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9768,14 +9790,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最強の三人だった。異論があるなら、またこのリングで証明しよう</t>
+          <t xml:space="preserve">まだ拳は握れる。…このリングは渡さないよ。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9790,7 +9812,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.bold[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9800,14 +9822,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞は受け取ろう。だが……次は旗ごともらいに行く。覚えておけ</t>
+          <t xml:space="preserve">三人が揃えば……どの団体にも、負ける道理はなかった</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9822,7 +9844,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.bold[2]</t>
+          <t xml:space="preserve">champion.composed.bold[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9832,14 +9854,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で満足する性分ではない。次は、全てを攫う</t>
+          <t xml:space="preserve">最強の三人だった。異論があるなら、またこのリングで証明しよう</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9854,7 +9876,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.bold[1]</t>
+          <t xml:space="preserve">defiant.composed.bold[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9864,14 +9886,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ようと……立っている者が、最後に語る権利を得る。今日はそれだけのこと</t>
+          <t xml:space="preserve">賞はもらっておくよ。でも……次は旗ごといただきに行くから。忘れないでよね</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9886,7 +9908,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.bold[2]</t>
+          <t xml:space="preserve">defiant.composed.bold[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9896,14 +9918,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。だが、拳を下ろす理由がどこにもなかった</t>
+          <t xml:space="preserve">この程度で満足できる性分じゃないんだ。次は、全部いただくよ。</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9913,12 +9935,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[1]</t>
+          <t xml:space="preserve">gauntlet.composed.bold[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9928,14 +9950,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝。…まあ、当然かな</t>
+          <t xml:space="preserve">何人来ようと……立っている者が、最後に語る権利を得る。今日はそれだけのこと</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9945,12 +9967,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.bold[1]</t>
+          <t xml:space="preserve">gauntlet.composed.bold[2]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9960,14 +9982,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。…でも、次は違う</t>
+          <t xml:space="preserve">身体は重い。でも、拳を下ろす理由がどこにもなかった</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9982,7 +10004,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.bold[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -9992,14 +10014,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然だね。…次も同じ</t>
+          <t xml:space="preserve">…優勝。…まあ、当然かな</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10014,7 +10036,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.bold[1]</t>
+          <t xml:space="preserve">postLose.composed.bold[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10024,14 +10046,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ上がある。…次は獲る</t>
+          <t xml:space="preserve">…悔しいね。…でも、次は違う</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10046,7 +10068,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10056,14 +10078,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後の一戦。…獲りにいくよ</t>
+          <t xml:space="preserve">…当然だね。…次も同じ</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10078,7 +10100,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">postWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10088,14 +10110,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝つよ。…それだけ</t>
+          <t xml:space="preserve">…まだ上がある。…次は獲る</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10110,7 +10132,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.bold[1]</t>
+          <t xml:space="preserve">preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10120,14 +10142,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選ばれたか。…まあ、当然だろうね</t>
+          <t xml:space="preserve">…最後の一戦。…獲りにいくよ</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10137,12 +10159,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10152,14 +10174,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…手加減はしない。…覚悟して</t>
+          <t xml:space="preserve">…勝つよ。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.bold[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10169,12 +10191,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">summon.composed.bold[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10184,14 +10206,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…獲った。…ここが頂点か。…悪くないね</t>
+          <t xml:space="preserve">…選ばれたか。…まあ、当然だろうね</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10201,7 +10223,7 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
@@ -10216,14 +10238,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…格の違い、見せてあげるよ</t>
+          <t xml:space="preserve">…手加減はしない。…覚悟して</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10233,12 +10255,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10248,14 +10270,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…手加減はしない。覚悟してね</t>
+          <t xml:space="preserve">…獲った。…ここが頂点か。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10265,7 +10287,7 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
@@ -10280,14 +10302,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるか。…まあ、賢い判断かもね</t>
+          <t xml:space="preserve">…格の違い、見せてあげるよ</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10297,12 +10319,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10312,14 +10334,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けた。…でも、次はこうはいかないよ</t>
+          <t xml:space="preserve">…手加減はしない。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10329,12 +10351,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10344,14 +10366,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だよ。…もう少し手応えが欲しかったけどね</t>
+          <t xml:space="preserve">…逃げるか。…まあ、賢い判断かもね</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.bold[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10361,12 +10383,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">result_lose.composed.bold[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10376,14 +10398,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だよ。…うちを甘く見ないでね</t>
+          <t xml:space="preserve">…負けた。…でも、次はこうはいかないよ</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.bold[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10393,12 +10415,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">result_win.composed.bold[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10408,14 +10430,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなもんかな。…まだまだ行けるよ</t>
+          <t xml:space="preserve">…当然の結果だよ。…もう少し手応えが欲しかったけどね</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10425,29 +10447,29 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点か。…でもまだ先がある気がするね</t>
+          <t xml:space="preserve">…当然の結果だよ。…うちを甘く見ないでね</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10457,59 +10479,123 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
+          <t xml:space="preserve">…こんなもんかな。…まだまだ行けるよ</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…頂点か。…でもまだ先がある気がするね</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.bold[1]</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr" s="2">
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr" s="12">
+      <c r="D320" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr" s="2">
+      <c r="E320" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr" s="3">
+      <c r="F320" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…目は確かみたいだね。まぁ…頑張るよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H318"/>
+  <autoFilter ref="A1:H320"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H327"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3874,7 +3874,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.composed.bold[1]</t>
+          <t xml:space="preserve">decline_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3899,14 +3899,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど。まあ…分かってくれるなら、それでいい。やるよ。</t>
+          <t xml:space="preserve">…それでいい。下がった分は、リングで取り返すよ。それだけなんだ。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.composed.bold[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.composed.bold[1]</t>
+          <t xml:space="preserve">decline_hold.composed.bold[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ゼロじゃないなら…まあ、いいよ。次はもう少し期待してる。</t>
+          <t xml:space="preserve">情けは要らない、って言うつもりだったんだ。……言えなかったよ。…借りにしておく。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.composed.bold[1]</t>
+          <t xml:space="preserve">decline_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。まあいいけど…次は、ないよ。覚えておいて。</t>
+          <t xml:space="preserve">下げる、か。構わないよ。ただ、どこを見てそう決めたのかは聞かせてもらうよ。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.composed.bold[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.composed.bold[1]</t>
+          <t xml:space="preserve">decline_strict.composed.bold[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。{tenure}率直に言うね。{record}この額は…ちょっと寂しいかな。</t>
+          <t xml:space="preserve">……そこまで削るんだ。いいよ、受け取る。……今の判断、こっちも覚えておくよ。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.composed.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -4027,14 +4027,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。…まあいいよ。ただ…我慢にも限度がある。それだけ。</t>
+          <t xml:space="preserve">潔いね、社長も。……いいよ、その額で。……安く使えると思ったら、痛い目見るんだ。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.composed.bold[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.bold[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.composed.bold[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4059,14 +4059,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…もう無理だよ。お世話になりました…とは、正直言えないかな。</t>
+          <t xml:space="preserve">……下げろって言ったんだ。……ふぅん。……なら、額に見合う体に戻すまでだよ。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.bold[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.bold[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4091,14 +4091,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう決めた。ここにいる理由が、なくなったから。…じゃあね。</t>
+          <t xml:space="preserve">先に言っておくんだ。今の私に、去年の額は重いよ。…削っていい。実力で取り返すから。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.composed.bold[1]</t>
+          <t xml:space="preserve">raise_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4123,14 +4123,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…もっと上で闘いたい。ここじゃ、物足りなくてね。</t>
+          <t xml:space="preserve">…なるほど。まあ…分かってくれるなら、それでいい。やるよ。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.composed.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.bold[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4155,14 +4155,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長。{tenure}決めたよ。…出る。特に未練はない。</t>
+          <t xml:space="preserve">…ゼロじゃないなら…まあ、いいよ。次はもう少し期待してる。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.bold[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.composed.bold[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.bold[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そうなるだろうとは思ってた。{rivalry}…じゃあね、社長。</t>
+          <t xml:space="preserve">…ふぅん。まあいいけど…次は、ないよ。覚えておいて。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.composed.bold[1]</t>
+          <t xml:space="preserve">raise_open.composed.bold[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4219,14 +4219,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪いけど、もう決めた。…変わらないよ。</t>
+          <t xml:space="preserve">…社長。{tenure}率直に言うね。{record}この額は…ちょっと寂しいかな。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.bold[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.bold[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.composed.bold[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.bold[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4251,369 +4251,369 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そこまで言うなら…まあ、もう少し付き合うよ。</t>
+          <t xml:space="preserve">…そう。…まあいいよ。ただ…我慢にも限度がある。それだけ。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長。…もう無理だよ。お世話になりました…とは、正直言えないかな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.bold[2]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.bold[2]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もう決めた。ここにいる理由が、なくなったから。…じゃあね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…もっと上で闘いたい。ここじゃ、物足りなくてね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…社長。{tenure}決めたよ。…出る。特に未練はない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…まあ、そうなるだろうとは思ってた。{rivalry}…じゃあね、社長。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…悪いけど、もう決めた。…変わらないよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そこまで言うなら…まあ、もう少し付き合うよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.bold[1]</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr" s="12">
+      <c r="D130" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.composed.bold[1]</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr" s="2">
+      <c r="E130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr" s="3">
+      <c r="F130" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…悪いけど、ここを離れる気はないよ。
 今の仲間がいるから</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.bold[1]</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
+      <c r="D131" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.composed.bold[1]</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="E131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F131" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…ここが居場所だから。
 悪いね</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.start.composed.bold[1]</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
+      <c r="D132" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">start.composed.bold[1]</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr" s="2">
+      <c r="E132" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr" s="3">
+      <c r="F132" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…引き抜き？ …面白いね。条件を聞こうか</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.success.composed.bold[1]</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="D133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">success.composed.bold[1]</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr" s="2">
+      <c r="E133" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr" s="3">
+      <c r="F133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…いいよ、行く。
 実力で示すだけだ</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長。うちの子たちにも、もう少し目を向けてほしいんだ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次のメインカード、私たちで組ませてください。今ならハマります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの給与、一度見直しの俎上に乗せてもらえませんか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちが積み上げてきたもの、評価の俎上に乗っていますか。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、ありがとうございます。その言葉、胸に留めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="40" customHeight="1">
-      <c r="A132" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…わかった。言うだけは言ったんだ、それでいいよ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="40" customHeight="1">
-      <c r="A133" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.bold[1]</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…なるほど、そういう形なんだ。ありがたく受け取っておくよ。</t>
-        </is>
-      </c>
-    </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.bold[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.bold[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4638,14 +4638,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがたく頂いておくよ。期待はきっちり超えてみせるから、見てて。</t>
+          <t xml:space="preserve">社長。うちの子たちにも、もう少し目を向けてほしいんだ。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.bold[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.bold[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4670,14 +4670,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。次の機会を待ちます。</t>
+          <t xml:space="preserve">社長、次のメインカード、私たちで組ませてください。今ならハマります。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.bold[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.bold[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4702,14 +4702,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そういう形ですか。お預かりします。</t>
+          <t xml:space="preserve">社長、私たちの給与、一度見直しの俎上に乗せてもらえませんか。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.bold[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.bold[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.bold[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4734,14 +4734,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。気持ちが引き締まります。</t>
+          <t xml:space="preserve">社長、私たちが積み上げてきたもの、評価の俎上に乗っていますか。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。次の機会に、また話します。</t>
+          <t xml:space="preserve">社長、ありがとうございます。その言葉、胸に留めます。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4798,14 +4798,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、そこまで気を回してくれたんだ。素直に甘えておこうかな。</t>
+          <t xml:space="preserve">…わかった。言うだけは言ったんだ、それでいいよ。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4830,14 +4830,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。その言葉、励みにします。</t>
+          <t xml:space="preserve">…なるほど、そういう形なんだ。ありがたく受け取っておくよ。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4862,14 +4862,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そう。なら引くよ。言いたいことは伝わったはずだ。</t>
+          <t xml:space="preserve">ありがたく頂いておくよ。期待はきっちり超えてみせるから、見てて。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4894,14 +4894,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん、そう来たんだ。せっかくだし、遠慮なくもらっておこうかな。</t>
+          <t xml:space="preserve">…承知しました。次の機会を待ちます。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4926,14 +4926,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました、次は声をかけます。</t>
+          <t xml:space="preserve">…なるほど、そういう形ですか。お預かりします。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4958,14 +4958,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも、大事ですから。</t>
+          <t xml:space="preserve">社長、ありがとうございます。気持ちが引き締まります。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4990,14 +4990,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました、注意します。</t>
+          <t xml:space="preserve">…承知しました。次の機会に、また話します。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -5022,14 +5022,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…なるほど、そこまで気を回してくれたんだ。素直に甘えておこうかな。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5054,14 +5054,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。営業に響くなら線を引きます。</t>
+          <t xml:space="preserve">ありがとうございます。その言葉、励みにします。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5086,14 +5086,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
+          <t xml:space="preserve">…そう。なら引くよ。言いたいことは伝わったはずだ。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5118,14 +5118,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご迷惑をおかけしました。明日から、しっかり出ます。</t>
+          <t xml:space="preserve">…ふぅん、そう来たんだ。せっかくだし、遠慮なくもらっておこうかな。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5150,14 +5150,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。次は、しっかりやります。</t>
+          <t xml:space="preserve">…承知しました、次は声をかけます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5182,14 +5182,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…へえ、そういうことか。その気遣い、ありがたく乗らせてもらうよ。</t>
+          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも、大事ですから。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5214,14 +5214,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。少し、休ませてもらいます。</t>
+          <t xml:space="preserve">…承知しました、注意します。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5246,14 +5246,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫です。まだ、いけます。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5278,14 +5278,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、メンバーケアですか。私も助かります。</t>
+          <t xml:space="preserve">…承知しました。営業に響くなら線を引きます。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5310,14 +5310,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。私からメンバーに話します。</t>
+          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5342,14 +5342,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。穏便に収めます。</t>
+          <t xml:space="preserve">…ご迷惑をおかけしました。明日から、しっかり出ます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮ありがとうございます。下の子のフォロー、助かります。</t>
+          <t xml:space="preserve">…ありがとうございます。次は、しっかりやります。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5406,14 +5406,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。態度、改めます。</t>
+          <t xml:space="preserve">…へえ、そういうことか。その気遣い、ありがたく乗らせてもらうよ。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（小さく頷いて、それ以上は語らなかった）</t>
+          <t xml:space="preserve">…ありがとうございます。少し、休ませてもらいます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5470,14 +5470,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…その心遣い、素直に嬉しいよ。</t>
+          <t xml:space="preserve">…大丈夫です。まだ、いけます。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5502,14 +5502,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。怪我させては元も子もないですね。緩めます。</t>
+          <t xml:space="preserve">…なるほど、メンバーケアですか。私も助かります。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5534,14 +5534,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。このまま続けます。</t>
+          <t xml:space="preserve">…承知しました。私からメンバーに話します。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5566,14 +5566,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なるほど、下の子たちのケアってわけだ。その心遣いには感謝するよ。</t>
+          <t xml:space="preserve">…ありがとうございます。穏便に収めます。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5583,12 +5583,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.attack.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5598,14 +5598,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう、同じ場所には立てない</t>
+          <t xml:space="preserve">…ご配慮ありがとうございます。下の子のフォロー、助かります。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.defend.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5630,14 +5630,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいね、受けて立つ</t>
+          <t xml:space="preserve">…承知しました。態度、改めます。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5647,29 +5647,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、まだ先がある。ここからだよ</t>
+          <t xml:space="preserve">（小さく頷いて、それ以上は語らなかった）</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5679,29 +5679,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…なるほど。…これが、その先か——）</t>
+          <t xml:space="preserve">…その心遣い、素直に嬉しいよ。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5711,29 +5711,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.bold[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…天井か。…でもまあ、ここまで来たんだし上出来だよ</t>
+          <t xml:space="preserve">…承知しました。怪我させては元も子もないですね。緩めます。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5743,29 +5743,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.bold[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂が見えてきた。もうひと踏ん張り、かな</t>
+          <t xml:space="preserve">…ありがとうございます。このまま続けます。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.bold[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5775,29 +5775,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.composed.bold[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.bold[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…通過点、だね。まだ先がある</t>
+          <t xml:space="preserve">…なるほど、下の子たちのケアってわけだ。その心遣いには感謝するよ。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.bold[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.composed</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5807,29 +5807,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.composed.bold[1]</t>
+          <t xml:space="preserve">bold.attack.composed</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。なかなかの景色じゃない</t>
+          <t xml:space="preserve">もう、同じ場所には立てない</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.bold[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.composed</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5839,29 +5839,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.composed.bold[1]</t>
+          <t xml:space="preserve">bold.defend.composed</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、当然っちゃ当然かな</t>
+          <t xml:space="preserve">いいね、受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.bold[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5886,14 +5886,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、みんなが見てるなら、格好つけないとね</t>
+          <t xml:space="preserve">…ま、まだ先がある。ここからだよ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
@@ -5918,14 +5918,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えない。…こういうこともあるか</t>
+          <t xml:space="preserve">（…なるほど。…これが、その先か——）</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.bold[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">cap_reached.composed.bold[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5950,14 +5950,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…目が覚めた。…ここで終わるのは、つまらないね</t>
+          <t xml:space="preserve">…天井か。…でもまあ、ここまで来たんだし上出来だよ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.bold[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.bold[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5982,14 +5982,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…待たせたね。…ここからだよ</t>
+          <t xml:space="preserve">…頂が見えてきた。もうひと踏ん張り、かな</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.composed.bold[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.bold[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -6014,14 +6014,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなはずじゃないんだけど。…焦ってはいないよ</t>
+          <t xml:space="preserve">…通過点、だね。まだ先がある</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.bold[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.composed.bold[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.bold[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6046,14 +6046,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…治ったはず、なんだけどね。…もたついてる</t>
+          <t xml:space="preserve">…ふぅん。なかなかの景色じゃない</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.bold[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.composed.bold[1]</t>
+          <t xml:space="preserve">pop_growth.composed.bold[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6078,14 +6078,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…怯えてる？ …まさかね。…まさか</t>
+          <t xml:space="preserve">…ま、当然っちゃ当然かな</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.bold[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.bold[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.composed.bold[1]</t>
+          <t xml:space="preserve">pop_star.composed.bold[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6110,14 +6110,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体は大丈夫。…気持ちだけが、まだ追いつかない</t>
+          <t xml:space="preserve">…ま、みんなが見てるなら、格好つけないとね</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6127,29 +6127,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この対抗戦は私たちが制した。次も同じだ。</t>
+          <t xml:space="preserve">…燃えない。…こういうこともあるか</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.bold[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6159,29 +6159,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい試合だった。出し惜しみなんてできなかったよ</t>
+          <t xml:space="preserve">…目が覚めた。…ここで終わるのは、つまらないね</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.bold[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6191,29 +6191,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが頂点。渡す気はないよ</t>
+          <t xml:space="preserve">…待たせたね。…ここからだよ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.bold[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6223,29 +6223,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.bold[1]</t>
+          <t xml:space="preserve">defeat.composed.bold[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全部やりきった。悔いはないよ</t>
+          <t xml:space="preserve">…こんなはずじゃないんだけど。…焦ってはいないよ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.bold[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6255,29 +6255,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.composed.bold[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.bold[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…リングの外でも、やるべきことをやっただけだよ</t>
+          <t xml:space="preserve">…治ったはず、なんだけどね。…もたついてる</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.bold[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6287,29 +6287,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.bold[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.bold[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、結果は出したからね。…でもまだ先がある</t>
+          <t xml:space="preserve">…怯えてる？ …まさかね。…まさか</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.bold[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.bold[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6319,29 +6319,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.bold[1]</t>
+          <t xml:space="preserve">penalty_end.composed.bold[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…通過点だね。次を見てなよ</t>
+          <t xml:space="preserve">…体は大丈夫。…気持ちだけが、まだ追いつかない</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.composed.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6366,14 +6366,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">春の頂点は私たちのもの。次も譲る気はない。</t>
+          <t xml:space="preserve">この対抗戦は私たちが制した。次も同じだ。</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">bestMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6398,14 +6398,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム、か。…燃えてきたな</t>
+          <t xml:space="preserve">…いい試合だった。出し惜しみなんてできなかったよ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6430,14 +6430,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるべきことは分かってる。全力でぶつかる</t>
+          <t xml:space="preserve">…ここが頂点。渡す気はないよ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.bold[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[3]</t>
+          <t xml:space="preserve">hallOfFame.composed.bold[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6462,14 +6462,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この闘志、ドームで全部見せてあげるよ</t>
+          <t xml:space="preserve">…全部やりきった。悔いはないよ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.bold[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">mediaAward.composed.bold[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6494,14 +6494,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。…達成感しかない</t>
+          <t xml:space="preserve">…リングの外でも、やるべきことをやっただけだよ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.bold[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">mvp.composed.bold[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6526,14 +6526,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力でやった。それが報われた</t>
+          <t xml:space="preserve">…まあ、結果は出したからね。…でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.bold[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[3]</t>
+          <t xml:space="preserve">rookie.composed.bold[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6558,14 +6558,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと上を目指す</t>
+          <t xml:space="preserve">…通過点だね。次を見てなよ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6575,29 +6575,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.bold[1]</t>
+          <t xml:space="preserve">springTagChampion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ先がある。焦らず行くよ</t>
+          <t xml:space="preserve">春の頂点は私たちのもの。次も譲る気はない。</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6607,29 +6607,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないチームだよ。居心地がいい</t>
+          <t xml:space="preserve">ドーム、か。…燃えてきたな</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6639,29 +6639,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この程度なら大丈夫。慌てないで</t>
+          <t xml:space="preserve">…やるべきことは分かってる。全力でぶつかる</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6671,29 +6671,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないね。この期待に応えるだけだよ</t>
+          <t xml:space="preserve">この闘志、ドームで全部見せてあげるよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6703,29 +6703,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいる意味、少し考え直してもいいかな</t>
+          <t xml:space="preserve">満員。…達成感しかない</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6735,29 +6735,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、少し立ち止まってるだけだよ。…たぶん</t>
+          <t xml:space="preserve">全力でやった。それが報われた</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.bold[3]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6767,29 +6767,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[3]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ先がある。…ここでなら</t>
+          <t xml:space="preserve">次はもっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.composed.bold[1]</t>
+          <t xml:space="preserve">N1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6814,14 +6814,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。…まあ、いいけど</t>
+          <t xml:space="preserve">…まだ先がある。焦らず行くよ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.bold[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.composed.bold[1]</t>
+          <t xml:space="preserve">N2.composed.bold[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6846,14 +6846,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やるね。…でも、まだ負けるつもりはない</t>
+          <t xml:space="preserve">…悪くないチームだよ。居心地がいい</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.bold[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.composed.bold[1]</t>
+          <t xml:space="preserve">N3.composed.bold[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6878,14 +6878,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。…まだ順番が来ないか</t>
+          <t xml:space="preserve">…この程度なら大丈夫。慌てないで</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.bold[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.composed.bold[1]</t>
+          <t xml:space="preserve">N4.composed.bold[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6910,14 +6910,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…使ってくれないと、困るんだけど</t>
+          <t xml:space="preserve">…悪くないね。この期待に応えるだけだよ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.bold[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.composed.bold[1]</t>
+          <t xml:space="preserve">N5_low.composed.bold[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6942,14 +6942,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、いいんだけどね。一人でも</t>
+          <t xml:space="preserve">…ここにいる意味、少し考え直してもいいかな</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.bold[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.composed.bold[1]</t>
+          <t xml:space="preserve">N5_warning.composed.bold[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6974,14 +6974,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くんだ。…まあ、{name2}が決めたことだからね</t>
+          <t xml:space="preserve">…ま、少し立ち止まってるだけだよ。…たぶん</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.composed.bold[1]</t>
+          <t xml:space="preserve">breakthrough.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -7006,14 +7006,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…でも、まだだね</t>
+          <t xml:space="preserve">…まだ先がある。…ここでなら</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.composed.bold[1]</t>
+          <t xml:space="preserve">G1.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7038,14 +7038,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は返す。…覚えておいて</t>
+          <t xml:space="preserve">…ふぅん。…まあ、いいけど</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.composed.bold[1]</t>
+          <t xml:space="preserve">G2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7070,14 +7070,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。…うちの看板、守れたかな</t>
+          <t xml:space="preserve">…やるね。…でも、まだ負けるつもりはない</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7087,29 +7087,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.composed.bold[1]</t>
+          <t xml:space="preserve">G3.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。結果で返すよ</t>
+          <t xml:space="preserve">…ふぅん。…まだ順番が来ないか</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7119,29 +7119,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.composed.bold[1]</t>
+          <t xml:space="preserve">G4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。しっかり追い込むよ</t>
+          <t xml:space="preserve">…使ってくれないと、困るんだけど</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7151,29 +7151,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.composed.bold[1]</t>
+          <t xml:space="preserve">R2.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…信じてくれるなら、応えないとね</t>
+          <t xml:space="preserve">…まあ、いいんだけどね。一人でも</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7183,29 +7183,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.composed.bold[1]</t>
+          <t xml:space="preserve">R3.modal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ終わってないよ。やるだけやる</t>
+          <t xml:space="preserve">…行くんだ。…まあ、{name2}が決めたことだからね</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7215,29 +7215,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.bold[1]</t>
+          <t xml:space="preserve">R4.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……納得はしていない。それだけは言っておくよ</t>
+          <t xml:space="preserve">…勝った。…でも、まだだね</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7247,29 +7247,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.composed.bold[1]</t>
+          <t xml:space="preserve">R5.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。任せて</t>
+          <t xml:space="preserve">…次は返す。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7279,29 +7279,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.composed.bold[1]</t>
+          <t xml:space="preserve">warVictory.voice.composed.bold[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい雰囲気だね。こういうのも大事だよ</t>
+          <t xml:space="preserve">…勝った。…うちの看板、守れたかな</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.composed.bold[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.composed.bold[1]</t>
+          <t xml:space="preserve">bonus.composed.bold[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…充電してくるよ。戻ったらまた行こう</t>
+          <t xml:space="preserve">…ありがとう。結果で返すよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.composed.bold[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.composed.bold[1]</t>
+          <t xml:space="preserve">camp.composed.bold[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7358,14 +7358,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…早く戻るよ。ありがとう</t>
+          <t xml:space="preserve">…いい機会だね。しっかり追い込むよ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.composed.bold[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.composed.bold[1]</t>
+          <t xml:space="preserve">encourage_high_trust.composed.bold[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7390,14 +7390,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。無駄にはしないよ</t>
+          <t xml:space="preserve">…信じてくれるなら、応えないとね</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.composed.bold[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7407,12 +7407,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.bold[1]</t>
+          <t xml:space="preserve">encourage.composed.bold[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7422,14 +7422,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くないね。いつも通りやるよ</t>
+          <t xml:space="preserve">…まだ終わってないよ。やるだけやる</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.bold[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.bold[1]</t>
+          <t xml:space="preserve">faction_decree.composed.bold[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7454,14 +7454,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない条件なんだよね。…少し考えてもいいかな</t>
+          <t xml:space="preserve">……納得はしていない。それだけは言っておくよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.composed.bold[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.bold[1]</t>
+          <t xml:space="preserve">media.composed.bold[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7486,14 +7486,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出してもらえないのに、練習する意味あるのかな</t>
+          <t xml:space="preserve">…いい機会だね。任せて</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.composed.bold[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.bold[2]</t>
+          <t xml:space="preserve">party.composed.bold[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7518,14 +7518,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…リングに上がれないなら、同じことだよ</t>
+          <t xml:space="preserve">…いい雰囲気だね。こういうのも大事だよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.composed.bold[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.bold[1]</t>
+          <t xml:space="preserve">refresh_leave.composed.bold[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7550,14 +7550,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「…この扱いは、さすがに通らないよ」と静かに言い切り、場が凍りついた）</t>
+          <t xml:space="preserve">…充電してくるよ。戻ったらまた行こう</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.composed.bold[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.bold[1]</t>
+          <t xml:space="preserve">special_treatment.composed.bold[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7582,14 +7582,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「…このまま終わるつもりはないよ」と静かな宣言を投稿）</t>
+          <t xml:space="preserve">…早く戻るよ。ありがとう</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.composed.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.bold[1]</t>
+          <t xml:space="preserve">trainer.composed.bold[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7614,14 +7614,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルト、狙わせてもらうよ。組んでくれる？</t>
+          <t xml:space="preserve">…いい機会だね。無駄にはしないよ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.bold[1]</t>
+          <t xml:space="preserve">E1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7646,14 +7646,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決着をつけたいんだ。組んでくれないかな</t>
+          <t xml:space="preserve">…悪くないね。いつも通りやるよ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.bold[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.bold[1]</t>
+          <t xml:space="preserve">E6.composed.bold[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7678,14 +7678,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…体が限界みたいだ。少し休むよ</t>
+          <t xml:space="preserve">…悪くない条件なんだよね。…少し考えてもいいかな</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.bold[1]</t>
+          <t xml:space="preserve">S_boycott.composed.bold[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7710,14 +7710,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このままだと先がないよ。考え直してくれないかな</t>
+          <t xml:space="preserve">…出してもらえないのに、練習する意味あるのかな</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.bold[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.bold[1]</t>
+          <t xml:space="preserve">S_boycott.composed.bold[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7742,14 +7742,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（拳を握り、それから静かに息を吐いた）</t>
+          <t xml:space="preserve">…リングに上がれないなら、同じことだよ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.bold[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.bold[1]</t>
+          <t xml:space="preserve">S_grumble.composed.bold[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7774,14 +7774,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し上に行きたい。特訓させてくれないかな</t>
+          <t xml:space="preserve">（「…この扱いは、さすがに通らないよ」と静かに言い切り、場が凍りついた）</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.bold[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.bold[1]</t>
+          <t xml:space="preserve">S_sns.composed.bold[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7806,14 +7806,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩に伝えておきたいことがあるんだ。任せてくれないかな</t>
+          <t xml:space="preserve">（SNSに「…このまま終わるつもりはないよ」と静かな宣言を投稿）</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.bold[1]</t>
+          <t xml:space="preserve">S1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7838,14 +7838,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、こういうこともあるよ。少し待ってて</t>
+          <t xml:space="preserve">…ベルト、狙わせてもらうよ。組んでくれる？</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.bold[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.bold[1]</t>
+          <t xml:space="preserve">S2.composed.bold[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7870,14 +7870,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪いけど、あの人とはちょっと厳しいかな</t>
+          <t xml:space="preserve">…決着をつけたいんだ。組んでくれないかな</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.bold[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7887,12 +7887,12 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.bold[1]</t>
+          <t xml:space="preserve">S3.composed.bold[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7902,14 +7902,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…私は私のやり方を変えるつもりはないよ。それだけ</t>
+          <t xml:space="preserve">…体が限界みたいだ。少し休むよ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.bold[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.bold[1]</t>
+          <t xml:space="preserve">S4_direct.composed.bold[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7934,14 +7934,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悪くない組み合わせだね。いいものにしよう</t>
+          <t xml:space="preserve">…このままだと先がないよ。考え直してくれないかな</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.bold[1]</t>
+          <t xml:space="preserve">S4_silent.composed.bold[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7966,14 +7966,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全国か。いい機会だね、自分のペースでやるよ</t>
+          <t xml:space="preserve">…………（拳を握り、それから静かに息を吐いた）</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.bold[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.bold[1]</t>
+          <t xml:space="preserve">S5.composed.bold[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の思い出を持って帰ってもらおうか</t>
+          <t xml:space="preserve">…もう少し上に行きたい。特訓させてくれないかな</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.bold[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.bold[2]</t>
+          <t xml:space="preserve">S6.composed.bold[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8030,14 +8030,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全員笑顔で帰す。…それが私の仕事だからね</t>
+          <t xml:space="preserve">…後輩に伝えておきたいことがあるんだ。任せてくれないかな</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.bold[1]</t>
+          <t xml:space="preserve">B1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8062,14 +8062,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ランウェイも私の舞台だよ。…全部持っていく</t>
+          <t xml:space="preserve">…まあ、こういうこともあるよ。少し待ってて</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.bold[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.bold[2]</t>
+          <t xml:space="preserve">B2_fighter1.composed.bold[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8094,14 +8094,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…プロレスもファッションも。…どっちも私のものだね</t>
+          <t xml:space="preserve">…悪いけど、あの人とはちょっと厳しいかな</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.bold[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.bold[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.bold[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8126,14 +8126,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…撮られるのは嫌いじゃないよ。いい写真にしよう</t>
+          <t xml:space="preserve">…私は私のやり方を変えるつもりはないよ。それだけ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.bold[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.bold[1]</t>
+          <t xml:space="preserve">B4_brand.composed.bold[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8158,14 +8158,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、自分のペースで話せばいいんでしょ。大丈夫</t>
+          <t xml:space="preserve">…悪くない組み合わせだね。いいものにしよう</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.bold[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.bold[1]</t>
+          <t xml:space="preserve">B4_cm.composed.bold[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8190,14 +8190,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい機会だね。自分らしくやらせてもらうよ</t>
+          <t xml:space="preserve">…全国か。いい機会だね、自分のペースでやるよ</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8207,29 +8207,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">B4_fan.composed.bold[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
+          <t xml:space="preserve">…最高の思い出を持って帰ってもらおうか</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.bold[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8239,29 +8239,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">B4_fan.composed.bold[2]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">…全員笑顔で帰す。…それが私の仕事だからね</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8271,29 +8271,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">B4_fashion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待には応える。見ていて</t>
+          <t xml:space="preserve">…ランウェイも私の舞台だよ。…全部持っていく</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.bold[2]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8303,29 +8303,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.bold[2]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">…プロレスもファッションも。…どっちも私のものだね</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.bold[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8335,29 +8335,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.bold[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点まで。…見ていて</t>
+          <t xml:space="preserve">…撮られるのは嫌いじゃないよ。いい写真にしよう</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.bold[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8367,29 +8367,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">B4_variety.composed.bold[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
+          <t xml:space="preserve">…まあ、自分のペースで話せばいいんでしょ。大丈夫</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.bold[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8399,29 +8399,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">B4.composed.bold[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…問題ない。少し休めば治る</t>
+          <t xml:space="preserve">…いい機会だね。自分らしくやらせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8446,14 +8446,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…片付いた相手だよ。…なのに、まだ目で追ってる</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8478,14 +8478,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった話らしいね。…じゃあ、この重さは何なんだろう</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8510,14 +8510,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
+          <t xml:space="preserve">…期待には応える。見ていて</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8549,7 +8549,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.bold[2]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8574,14 +8574,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…期待には応える。見ていて</t>
+          <t xml:space="preserve">…頂点まで。…見ていて</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8606,14 +8606,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
+          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8638,14 +8638,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
+          <t xml:space="preserve">…問題ない。少し休めば治る</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.bold[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.bold[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8670,14 +8670,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点まで。…見ていて</t>
+          <t xml:space="preserve">…片付いた相手だよ。…なのに、まだ目で追ってる</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.bold[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8702,14 +8702,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
+          <t xml:space="preserve">…終わった話らしいね。…じゃあ、この重さは何なんだろう</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.bold[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.bold[2]</t>
+          <t xml:space="preserve">draftInterest.composed.bold[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8734,14 +8734,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…問題ない。少し休めば治る</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。それだけ</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.bold[1]</t>
+          <t xml:space="preserve">draftJoin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8766,14 +8766,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.bold[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.bold[2]</t>
+          <t xml:space="preserve">draftJoin.composed.bold[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8798,14 +8798,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
+          <t xml:space="preserve">…期待には応える。見ていて</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">faGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8830,14 +8830,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
+          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.bold[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.bold[1]</t>
+          <t xml:space="preserve">faSigning.composed.bold[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8862,14 +8862,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…目は確かみたいだね。まぁ…頑張るよ</t>
+          <t xml:space="preserve">…てっぺんを獲りに来た。よろしく</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.bold[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.bold[1]</t>
+          <t xml:space="preserve">faWelcome.composed.bold[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8894,14 +8894,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
+          <t xml:space="preserve">…頂点まで。…見ていて</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.bold[1]</t>
+          <t xml:space="preserve">injury.composed.bold[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8926,14 +8926,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
+          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.bold[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.bold[1]</t>
+          <t xml:space="preserve">injury.composed.bold[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8958,14 +8958,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…取り返す。…覚えておいて</t>
+          <t xml:space="preserve">…問題ない。少し休めば治る</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.bold[1]</t>
+          <t xml:space="preserve">release.composed.bold[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8990,14 +8990,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
+          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.bold[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">release.composed.bold[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9022,14 +9022,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
+          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">rentalGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9054,14 +9054,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
+          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.bold[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9086,14 +9086,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
+          <t xml:space="preserve">…目は確かみたいだね。まぁ…頑張るよ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9125,7 +9125,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.bold[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">titleDefense.composed.bold[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9157,7 +9157,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">titleLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9189,7 +9189,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">titleWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9221,7 +9221,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9231,29 +9231,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…無理なものは無理。…それだけ</t>
+          <t xml:space="preserve">…悔しいね。でも、必ず戻ってくる</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.bold[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9263,29 +9263,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…壁作ってない？ …まあ、いいけど</t>
+          <t xml:space="preserve">…これで終わりじゃない。次で証明する</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9295,29 +9295,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なかなかやるね。認めてあげてもいいかな</t>
+          <t xml:space="preserve">…レンタルでも全力。当然だね</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9327,29 +9327,29 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の相棒だね。…二人なら怖いものはない</t>
+          <t xml:space="preserve">…認める。…でもこの借りは返す</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9359,29 +9359,29 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…終わった。…次に行くよ</t>
+          <t xml:space="preserve">…まだ渡さない。…当然だね</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9391,29 +9391,29 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…面白い相手だね。…超えてみせるよ</t>
+          <t xml:space="preserve">…取り返す。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9423,29 +9423,29 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.composed[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の敵だね。…超える。それだけ</t>
+          <t xml:space="preserve">…頂点。…でもまだ先がある</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9470,14 +9470,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…生涯の勝負だ。…望むところ</t>
+          <t xml:space="preserve">…無理なものは無理。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9502,14 +9502,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここが最高の場所だ。…もっと強くしてみせる</t>
+          <t xml:space="preserve">…壁作ってない？ …まあ、いいけど</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9534,14 +9534,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう付き合いきれないかな。…覚えておいて</t>
+          <t xml:space="preserve">…なかなかやるね。認めてあげてもいいかな</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9566,14 +9566,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この扱いは、ちょっとどうかと思うけど</t>
+          <t xml:space="preserve">…最高の相棒だね。…二人なら怖いものはない</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.composed[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9598,14 +9598,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻ったね。…あの感覚は覚えた</t>
+          <t xml:space="preserve">…終わった。…次に行くよ</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9615,29 +9615,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は重い。でも、最後の舞台を降りる理由にはならないよ</t>
+          <t xml:space="preserve">…面白い相手だね。…超えてみせるよ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9647,29 +9647,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.bold[2]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た者だけが立てる場所だ。…受けて立つ</t>
+          <t xml:space="preserve">…最高の敵だね。…超える。それだけ</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9679,29 +9679,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.composed[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰でも、受けて立つよ。慌てる場面じゃない</t>
+          <t xml:space="preserve">…生涯の勝負だ。…望むところ</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.composed[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9711,29 +9711,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.bold[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.composed[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人でも並びなよ。…上等。並んだだけ、倒すから</t>
+          <t xml:space="preserve">…ここが最高の場所だ。…もっと強くしてみせる</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.composed[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9743,29 +9743,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.bold[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.composed[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人片づけたよ。息は上がってるけど、退く場面じゃない。次、来なよ</t>
+          <t xml:space="preserve">…もう付き合いきれないかな。…覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.composed[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9775,29 +9775,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.bold[2]</t>
+          <t xml:space="preserve">trust_below_35.bold.composed[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ拳は握れる。…このリングは渡さないよ。次は誰だ</t>
+          <t xml:space="preserve">…この扱いは、ちょっとどうかと思うけど</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9807,29 +9807,29 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人が揃えば……どの団体にも、負ける道理はなかった</t>
+          <t xml:space="preserve">…戻ったね。…あの感覚は覚えた</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9839,12 +9839,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[2]</t>
+          <t xml:space="preserve">preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9854,14 +9854,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最強の三人だった。異論があるなら、またこのリングで証明しよう</t>
+          <t xml:space="preserve">…身体は重い。でも、最後の舞台を降りる理由にはならないよ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.bold[1]</t>
+          <t xml:space="preserve">preFinal.composed.bold[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9886,14 +9886,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっておくよ。でも……次は旗ごといただきに行くから。忘れないでよね</t>
+          <t xml:space="preserve">ここまで来た者だけが立てる場所だ。…受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.bold[2]</t>
+          <t xml:space="preserve">preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9918,14 +9918,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で満足できる性分じゃないんだ。次は、全部いただくよ。</t>
+          <t xml:space="preserve">相手が誰でも、受けて立つよ。慌てる場面じゃない</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.bold[1]</t>
+          <t xml:space="preserve">preMatch.composed.bold[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9950,14 +9950,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ようと……立っている者が、最後に語る権利を得る。今日はそれだけのこと</t>
+          <t xml:space="preserve">何人でも並びなよ。…上等。並んだだけ、倒すから</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.bold[2]</t>
+          <t xml:space="preserve">survivor.composed.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9982,14 +9982,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。でも、拳を下ろす理由がどこにもなかった</t>
+          <t xml:space="preserve">…一人片づけたよ。息は上がってるけど、退く場面じゃない。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[1]</t>
+          <t xml:space="preserve">survivor.composed.bold[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10014,14 +10014,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝。…まあ、当然かな</t>
+          <t xml:space="preserve">まだ拳は握れる。…このリングは渡さないよ。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.bold[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10046,14 +10046,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。…でも、次は違う</t>
+          <t xml:space="preserve">三人が揃えば……どの団体にも、負ける道理はなかった</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.bold[1]</t>
+          <t xml:space="preserve">champion.composed.bold[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10078,14 +10078,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然だね。…次も同じ</t>
+          <t xml:space="preserve">最強の三人だった。異論があるなら、またこのリングで証明しよう</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.bold[1]</t>
+          <t xml:space="preserve">defiant.composed.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10110,14 +10110,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ上がある。…次は獲る</t>
+          <t xml:space="preserve">賞はもらっておくよ。でも……次は旗ごといただきに行くから。忘れないでよね</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">defiant.composed.bold[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10142,14 +10142,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後の一戦。…獲りにいくよ</t>
+          <t xml:space="preserve">この程度で満足できる性分じゃないんだ。次は、全部いただくよ。</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">gauntlet.composed.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10174,14 +10174,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝つよ。…それだけ</t>
+          <t xml:space="preserve">何人来ようと……立っている者が、最後に語る権利を得る。今日はそれだけのこと</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.bold[1]</t>
+          <t xml:space="preserve">gauntlet.composed.bold[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10206,14 +10206,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選ばれたか。…まあ、当然だろうね</t>
+          <t xml:space="preserve">身体は重い。でも、拳を下ろす理由がどこにもなかった</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10238,14 +10238,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…手加減はしない。…覚悟して</t>
+          <t xml:space="preserve">…優勝。…まあ、当然かな</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.bold[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">postLose.composed.bold[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10270,14 +10270,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…獲った。…ここが頂点か。…悪くないね</t>
+          <t xml:space="preserve">…悔しいね。…でも、次は違う</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10287,12 +10287,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10302,14 +10302,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…格の違い、見せてあげるよ</t>
+          <t xml:space="preserve">…当然だね。…次も同じ</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">postWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10334,14 +10334,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…手加減はしない。覚悟してね</t>
+          <t xml:space="preserve">…まだ上がある。…次は獲る</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10366,14 +10366,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるか。…まあ、賢い判断かもね</t>
+          <t xml:space="preserve">…最後の一戦。…獲りにいくよ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.bold[1]</t>
+          <t xml:space="preserve">preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10398,14 +10398,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けた。…でも、次はこうはいかないよ</t>
+          <t xml:space="preserve">…勝つよ。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.bold[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10415,12 +10415,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.bold[1]</t>
+          <t xml:space="preserve">summon.composed.bold[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10430,14 +10430,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だよ。…もう少し手応えが欲しかったけどね</t>
+          <t xml:space="preserve">…選ばれたか。…まあ、当然だろうね</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
@@ -10462,14 +10462,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だよ。…うちを甘く見ないでね</t>
+          <t xml:space="preserve">…手加減はしない。…覚悟して</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10494,14 +10494,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなもんかな。…まだまだ行けるよ</t>
+          <t xml:space="preserve">…獲った。…ここが頂点か。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10511,29 +10511,29 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点か。…でもまだ先がある気がするね</t>
+          <t xml:space="preserve">…格の違い、見せてあげるよ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10543,59 +10543,283 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
+          <t xml:space="preserve">…手加減はしない。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるか。…まあ、賢い判断かもね</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けた。…でも、次はこうはいかないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…当然の結果だよ。…もう少し手応えが欲しかったけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…当然の結果だよ。…うちを甘く見ないでね</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[2]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.bold[2]</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…こんなもんかな。…まだまだ行けるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…頂点か。…でもまだ先がある気がするね</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.bold[1]</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr" s="2">
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr" s="12">
+      <c r="D327" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr" s="2">
+      <c r="E327" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr" s="3">
+      <c r="F327" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…目は確かみたいだね。まぁ…頑張るよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H320"/>
+  <autoFilter ref="A1:H327"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
@@ -328,7 +328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H327"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9573,7 +9573,7 @@
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.composed.bold[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9598,14 +9598,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻ったね。…あの感覚は覚えた</t>
+          <t xml:space="preserve">…負けは負け。…でもいい試合だった</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9615,29 +9615,29 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…身体は重い。でも、最後の舞台を降りる理由にはならないよ</t>
+          <t xml:space="preserve">…上等。…これが実力だ</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.composed.bold[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9647,29 +9647,29 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.bold[2]</t>
+          <t xml:space="preserve">GL-01.loss.composed.bold[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来た者だけが立てる場所だ。…受けて立つ</t>
+          <t xml:space="preserve">…こんなはずじゃない。…次は返す</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.composed.bold[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9679,29 +9679,29 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">GL-01.win.composed.bold[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰でも、受けて立つよ。慌てる場面じゃない</t>
+          <t xml:space="preserve">…当然。…まだまだだけどね</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.composed.bold[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9711,29 +9711,29 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.bold[2]</t>
+          <t xml:space="preserve">GL-02.composed.bold[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人でも並びなよ。…上等。並んだだけ、倒すから</t>
+          <t xml:space="preserve">…まだまだ。もう一本</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.composed.bold[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9743,29 +9743,29 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.bold[1]</t>
+          <t xml:space="preserve">GL-03.down.composed.bold[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人片づけたよ。息は上がってるけど、退く場面じゃない。次、来なよ</t>
+          <t xml:space="preserve">…この扱いは、どうなの</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.composed.bold[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9775,29 +9775,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.bold[2]</t>
+          <t xml:space="preserve">GL-03.up.composed.bold[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ拳は握れる。…このリングは渡さないよ。次は誰だ</t>
+          <t xml:space="preserve">…ここ、いいね。…もっと盛り上げてやるよ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9807,29 +9807,29 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人が揃えば……どの団体にも、負ける道理はなかった</t>
+          <t xml:space="preserve">…戻ったね。…あの感覚は覚えた</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9839,12 +9839,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[2]</t>
+          <t xml:space="preserve">preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9854,14 +9854,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最強の三人だった。異論があるなら、またこのリングで証明しよう</t>
+          <t xml:space="preserve">…身体は重い。でも、最後の舞台を降りる理由にはならないよ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.bold[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.bold[1]</t>
+          <t xml:space="preserve">preFinal.composed.bold[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9886,14 +9886,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらっておくよ。でも……次は旗ごといただきに行くから。忘れないでよね</t>
+          <t xml:space="preserve">ここまで来た者だけが立てる場所だ。…受けて立つ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.bold[2]</t>
+          <t xml:space="preserve">preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9918,14 +9918,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で満足できる性分じゃないんだ。次は、全部いただくよ。</t>
+          <t xml:space="preserve">相手が誰でも、受けて立つよ。慌てる場面じゃない</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.bold[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.bold[1]</t>
+          <t xml:space="preserve">preMatch.composed.bold[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9950,14 +9950,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ようと……立っている者が、最後に語る権利を得る。今日はそれだけのこと</t>
+          <t xml:space="preserve">何人でも並びなよ。…上等。並んだだけ、倒すから</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.bold[2]</t>
+          <t xml:space="preserve">survivor.composed.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -9982,14 +9982,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。でも、拳を下ろす理由がどこにもなかった</t>
+          <t xml:space="preserve">…一人片づけたよ。息は上がってるけど、退く場面じゃない。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.bold[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.bold[1]</t>
+          <t xml:space="preserve">survivor.composed.bold[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10014,14 +10014,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…優勝。…まあ、当然かな</t>
+          <t xml:space="preserve">まだ拳は握れる。…このリングは渡さないよ。次は誰だ</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.bold[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10046,14 +10046,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいね。…でも、次は違う</t>
+          <t xml:space="preserve">三人が揃えば……どの団体にも、負ける道理はなかった</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.bold[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.bold[1]</t>
+          <t xml:space="preserve">champion.composed.bold[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10078,14 +10078,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然だね。…次も同じ</t>
+          <t xml:space="preserve">最強の三人だった。異論があるなら、またこのリングで証明しよう</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.bold[1]</t>
+          <t xml:space="preserve">defiant.composed.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10110,14 +10110,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ上がある。…次は獲る</t>
+          <t xml:space="preserve">賞はもらっておくよ。でも……次は旗ごといただきに行くから。忘れないでよね</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.bold[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.bold[1]</t>
+          <t xml:space="preserve">defiant.composed.bold[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10142,14 +10142,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後の一戦。…獲りにいくよ</t>
+          <t xml:space="preserve">この程度で満足できる性分じゃないんだ。次は、全部いただくよ。</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.bold[1]</t>
+          <t xml:space="preserve">gauntlet.composed.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10174,14 +10174,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝つよ。…それだけ</t>
+          <t xml:space="preserve">何人来ようと……立っている者が、最後に語る権利を得る。今日はそれだけのこと</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.bold[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.bold[1]</t>
+          <t xml:space="preserve">gauntlet.composed.bold[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10206,14 +10206,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…選ばれたか。…まあ、当然だろうね</t>
+          <t xml:space="preserve">身体は重い。でも、拳を下ろす理由がどこにもなかった</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">champion.composed.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10238,14 +10238,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…手加減はしない。…覚悟して</t>
+          <t xml:space="preserve">…優勝。…まあ、当然かな</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.bold[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">postLose.composed.bold[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10270,14 +10270,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…獲った。…ここが頂点か。…悪くないね</t>
+          <t xml:space="preserve">…悔しいね。…でも、次は違う</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10287,12 +10287,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10302,14 +10302,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…格の違い、見せてあげるよ</t>
+          <t xml:space="preserve">…当然だね。…次も同じ</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">postWin.composed.bold[1]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10334,14 +10334,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…手加減はしない。覚悟してね</t>
+          <t xml:space="preserve">…まだ上がある。…次は獲る</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="C313" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">preFinal.composed.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10366,14 +10366,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるか。…まあ、賢い判断かもね</t>
+          <t xml:space="preserve">…最後の一戦。…獲りにいくよ</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.bold[1]</t>
+          <t xml:space="preserve">preMatch.composed.bold[1]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10398,14 +10398,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けた。…でも、次はこうはいかないよ</t>
+          <t xml:space="preserve">…勝つよ。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.bold[1]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10415,12 +10415,12 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.bold[1]</t>
+          <t xml:space="preserve">summon.composed.bold[1]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10430,14 +10430,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だよ。…もう少し手応えが欲しかったけどね</t>
+          <t xml:space="preserve">…選ばれたか。…まあ、当然だろうね</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="C316" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D316" t="inlineStr" s="12">
@@ -10462,14 +10462,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…当然の結果だよ。…うちを甘く見ないでね</t>
+          <t xml:space="preserve">…手加減はしない。…覚悟して</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.bold[1]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="C317" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[2]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10494,14 +10494,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…こんなもんかな。…まだまだ行けるよ</t>
+          <t xml:space="preserve">…獲った。…ここが頂点か。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10511,29 +10511,29 @@
       </c>
       <c r="C318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頂点か。…でもまだ先がある気がするね</t>
+          <t xml:space="preserve">…格の違い、見せてあげるよ</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.bold[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10543,59 +10543,283 @@
       </c>
       <c r="C319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.bold[1]</t>
+          <t xml:space="preserve">composed.bold[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
+          <t xml:space="preserve">…手加減はしない。覚悟してね</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるか。…まあ、賢い判断かもね</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けた。…でも、次はこうはいかないよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…当然の結果だよ。…もう少し手応えが欲しかったけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…当然の結果だよ。…うちを甘く見ないでね</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.bold[2]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.bold[2]</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…こんなもんかな。…まだまだ行けるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…頂点か。…でもまだ先がある気がするね</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.bold[1]</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…空白は、結果で埋める。それだけだよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.bold[1]</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr" s="2">
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr" s="12">
+      <c r="D327" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.bold[1]</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr" s="2">
+      <c r="E327" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr" s="3">
+      <c r="F327" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…目は確かみたいだね。まぁ…頑張るよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H320"/>
+  <autoFilter ref="A1:H327"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
@@ -2331,7 +2331,7 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。……あの人は、私が引き受けるよ。</t>
+          <t xml:space="preserve">社長。……あの団体は、私たち三人で引き受けるよ。</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頼みがあるの。あの相手と、やらせてほしい。</t>
+          <t xml:space="preserve">頼みがあるの。あの団体へ、三人で行かせてほしい。</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……名前を挙げさせてもらうね。あの人と、やりたい。</t>
+          <t xml:space="preserve">……行き先を挙げさせてもらうね。三人で、あそこへ。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×強気.xlsx
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…承知しました。私からメンバーに話します。</t>
+          <t xml:space="preserve">…わかった。私からメンバーに話しておくよ。</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮ありがとうございます。下の子のフォロー、助かります。</t>
+          <t xml:space="preserve">…そこまで見てくれてるんだ。下の子のこと、助かるよ。</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
+          <t xml:space="preserve">…私の代わりは、そう簡単には見つからないよ</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…止まるわけにはいかない。すぐ戻る</t>
+          <t xml:space="preserve">…私の代わりは、そう簡単には見つからないよ</t>
         </is>
       </c>
     </row>
